--- a/inputs/fr/LiST countries/SYR_databook.xlsx
+++ b/inputs/fr/LiST countries/SYR_databook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\Nutrition\inputs\fr\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ECC9CA0-7AD7-4F6D-A0C0-109C4DA134D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B7E1ED-0356-4238-A7E9-FF1BABDD0005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3670" windowWidth="19200" windowHeight="6530" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Causes du décès" sheetId="3" r:id="rId3"/>
     <sheet name="Dist. de l'état nutritionnel" sheetId="4" r:id="rId4"/>
     <sheet name="Dist. l'allaitement maternel" sheetId="5" r:id="rId5"/>
-    <sheet name="Tendances temporelles" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Tendances temporelles" sheetId="6" r:id="rId6"/>
     <sheet name="Perte économique" sheetId="7" r:id="rId7"/>
     <sheet name="Paquets ANJE" sheetId="8" r:id="rId8"/>
     <sheet name="Traitement de la MAS" sheetId="9" r:id="rId9"/>
@@ -91,7 +91,7 @@
     <definedName name="term_SGA">'Données pop de l''année de ref'!$C$47</definedName>
     <definedName name="U5_mortality">'Données pop de l''année de ref'!$C$39</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -678,8 +678,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -692,8 +691,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
+OR = 0.89 for stunting [Panjwani et al. 2017 J Nutr</t>
         </r>
       </text>
     </comment>
@@ -834,35 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -876,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -890,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
+    <comment ref="E31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000010000000}">
       <text>
         <r>
           <rPr>
@@ -904,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
+    <comment ref="A34" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000011000000}">
       <text>
         <r>
           <rPr>
@@ -917,7 +887,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
+    <comment ref="A37" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000012000000}">
       <text>
         <r>
           <rPr>
@@ -930,7 +900,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
+    <comment ref="B44" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000013000000}">
       <text>
         <r>
           <rPr>
@@ -943,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
+    <comment ref="A51" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000014000000}">
       <text>
         <r>
           <rPr>
@@ -956,7 +926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
+    <comment ref="B52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000015000000}">
       <text>
         <r>
           <rPr>
@@ -969,35 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F52" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-Lassi et al 2020, RR 0.64 (0.44-0.92) 
-RR converted to OR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001A000000}">
+    <comment ref="B53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1011,7 +953,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001B000000}">
+    <comment ref="E53" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1025,7 +967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-00001C000000}">
+    <comment ref="E54" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1600-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1561,8 +1503,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -1732,8 +1673,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1746,8 +1686,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1760,8 +1699,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -1774,8 +1712,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2138,8 +2075,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Peña‐Rosas et al 2019, anemia RR 0.72 (0.54-0.97)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2152,7 +2088,8 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Insufficient published research on the intervention’s effect on the outcome.</t>
+Insufficient published research on the intervention’s effect on the outcome.
+Thereofre, set effect of rice = effect of wheat</t>
         </r>
       </text>
     </comment>
@@ -2165,8 +2102,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-Larson et al 2021, RR 0.80 (0.70-0.92)
-If no data for anaemia prev. the use RR otherwise convert RR to OR using prev.</t>
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -2192,8 +2128,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
         </r>
       </text>
     </comment>
@@ -2366,8 +2301,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2380,8 +2314,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2394,8 +2327,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2408,8 +2340,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
         </r>
       </text>
     </comment>
@@ -2660,7 +2591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000052000000}">
       <text>
         <r>
           <rPr>
@@ -2669,12 +2600,37 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RR from the lterature was used.
-RRR = 0.53 (0.40-0.70) for being anaemic [Hutton and Hassan, 2007 Jama [63]]</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000053000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+Zhao et al 2019, ≥6 months, RR 0.92 (0.87-0.99 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
       <text>
         <r>
           <rPr>
@@ -2688,7 +2644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000054000000}">
+    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
       <text>
         <r>
           <rPr>
@@ -2702,7 +2658,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000055000000}">
+    <comment ref="J50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
       <text>
         <r>
           <rPr>
@@ -2716,7 +2672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000056000000}">
+    <comment ref="K50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
       <text>
         <r>
           <rPr>
@@ -2730,7 +2686,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000057000000}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
       <text>
         <r>
           <rPr>
@@ -2744,7 +2700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000058000000}">
+    <comment ref="I51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -2758,7 +2714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000059000000}">
+    <comment ref="J51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -2772,7 +2728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005A000000}">
+    <comment ref="K51" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -2786,7 +2742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005B000000}">
+    <comment ref="H52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -2800,7 +2756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005C000000}">
+    <comment ref="I52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -2814,7 +2770,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005D000000}">
+    <comment ref="J52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -2828,7 +2784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005E000000}">
+    <comment ref="K52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00005F000000}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
       <text>
         <r>
           <rPr>
@@ -2856,7 +2812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000060000000}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
       <text>
         <r>
           <rPr>
@@ -2870,7 +2826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000061000000}">
+    <comment ref="J53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
       <text>
         <r>
           <rPr>
@@ -2884,7 +2840,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000062000000}">
+    <comment ref="K53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
       <text>
         <r>
           <rPr>
@@ -2898,7 +2854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000063000000}">
+    <comment ref="L54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
       <text>
         <r>
           <rPr>
@@ -2911,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000064000000}">
+    <comment ref="M54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
       <text>
         <r>
           <rPr>
@@ -2924,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000065000000}">
+    <comment ref="N54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000066000000}">
+    <comment ref="O54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
       <text>
         <r>
           <rPr>
@@ -2950,7 +2906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
+    <comment ref="L55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
       <text>
         <r>
           <rPr>
@@ -2963,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000068000000}">
+    <comment ref="M55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -2976,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000069000000}">
+    <comment ref="N55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -2989,7 +2945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006A000000}">
+    <comment ref="O55" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -3002,7 +2958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006B000000}">
+    <comment ref="L56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -3011,12 +2967,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006C000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -3025,12 +2980,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006D000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -3039,12 +2993,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006E000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
       <text>
         <r>
           <rPr>
@@ -3053,12 +3006,11 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Tharindu Wickramaarachchi:
-RRR = 0.83 (0.74-0.93) for being anaemic [Radeva‐Petrova et al. 2014, The Cochrane Library [77]]
-RRR was used</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00006F000000}">
+Moorthy et al 2020, anemia RR 0.90 (0.84-0.95 )</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
       <text>
         <r>
           <rPr>
@@ -3072,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000070000000}">
+    <comment ref="D58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
       <text>
         <r>
           <rPr>
@@ -3086,7 +3038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000071000000}">
+    <comment ref="E58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
       <text>
         <r>
           <rPr>
@@ -3100,7 +3052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000072000000}">
+    <comment ref="F58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
       <text>
         <r>
           <rPr>
@@ -3114,7 +3066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000073000000}">
+    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000074000000}">
+    <comment ref="H58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
       <text>
         <r>
           <rPr>
@@ -3142,7 +3094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000075000000}">
+    <comment ref="I58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
       <text>
         <r>
           <rPr>
@@ -3156,7 +3108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000076000000}">
+    <comment ref="J58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
       <text>
         <r>
           <rPr>
@@ -3170,7 +3122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000077000000}">
+    <comment ref="K58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
       <text>
         <r>
           <rPr>
@@ -3184,7 +3136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000078000000}">
+    <comment ref="L58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -3198,7 +3150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000079000000}">
+    <comment ref="M58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -3212,7 +3164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007A000000}">
+    <comment ref="N58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -3226,7 +3178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007B000000}">
+    <comment ref="O58" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -3240,7 +3192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007C000000}">
+    <comment ref="E59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -3253,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007D000000}">
+    <comment ref="F59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -3266,7 +3218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007E000000}">
+    <comment ref="G59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
       <text>
         <r>
           <rPr>
@@ -3279,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-00007F000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000081000000}">
       <text>
         <r>
           <rPr>
@@ -3292,7 +3244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000080000000}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000082000000}">
       <text>
         <r>
           <rPr>
@@ -3302,6 +3254,32 @@
           </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Wessells et al 2022, iron deficiency anemia), PR 0.36 (0.30-0.44) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000083000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000084000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t>Tharindu Wickramaarachchi:
+OR = 0.976 (0.975-0.978) for being anaemic [Barkley et al. 2015, B J Nutrition [80]]</t>
         </r>
       </text>
     </comment>
@@ -4373,7 +4351,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5023,7 +5001,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -5673,7 +5651,7 @@
             <rFont val="Arial"/>
           </rPr>
           <t>Nick Scott:
-RRR = 0.49 (0.29-0.82) for mortality due to prematurity [Lawn et al. 2010, I J Emi 2010[67]]</t>
+Sivanandan &amp; Sankar 2023, neonatal RR 0.68 (0.53-0.86)</t>
         </r>
       </text>
     </comment>
@@ -6941,9 +6919,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6955,9 +6932,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6969,9 +6945,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -6983,9 +6958,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7118,68 +7092,12 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Arial"/>
-          </rPr>
           <t xml:space="preserve">Tharindu Wickramaarachchi:
 Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -7192,7 +7110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+    <comment ref="E61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000010000000}">
       <text>
         <r>
           <rPr>
@@ -7205,7 +7123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+    <comment ref="E62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000011000000}">
       <text>
         <r>
           <rPr>
@@ -7218,6 +7136,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="F64" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+          </rPr>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A89" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-1300-000016000000}">
       <text>
         <r>
@@ -7239,9 +7209,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7253,9 +7222,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7267,9 +7235,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7281,9 +7248,8 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
           </rPr>
-          <t>Tharindu Wickramaarachchi:
-RR converted to an OR using BF prev.
-Lassi et al 2019, EIBF RR 1.56 (1.37-1.77)</t>
+          <t xml:space="preserve">Tharindu Wickramaarachchi:
+Mahumud et al 2022, EBF OR 1.73 (1.35-2.11) </t>
         </r>
       </text>
     </comment>
@@ -7370,7 +7336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="337">
   <si>
     <t>Field</t>
   </si>
@@ -9301,7 +9267,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="41">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9310,7 +9276,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="42">
-        <v>2030</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -9328,7 +9294,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="43">
-        <v>54217.94677734375</v>
+        <v>54304.55419921875</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9360,7 +9326,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="45">
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9368,7 +9334,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="45">
-        <v>0.77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9402,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="C17" s="45">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9410,7 +9376,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="45">
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9418,7 +9384,7 @@
         <v>29</v>
       </c>
       <c r="C19" s="45">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9427,7 +9393,7 @@
       </c>
       <c r="C20" s="46">
         <f>1-frac_rice-frac_wheat-frac_maize</f>
-        <v>0.20000000000000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9486,7 +9452,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="45">
-        <v>0.35675533525383901</v>
+        <v>0.34994163924792399</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9494,7 +9460,7 @@
         <v>38</v>
       </c>
       <c r="C30" s="99">
-        <v>6.5910586704521698E-2</v>
+        <v>0.10516916316476101</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9502,7 +9468,7 @@
         <v>39</v>
       </c>
       <c r="C31" s="99">
-        <v>9.262041217609189E-2</v>
+        <v>8.4505866375242988E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9510,7 +9476,7 @@
         <v>40</v>
       </c>
       <c r="C32" s="99">
-        <v>0.48471366586554798</v>
+        <v>0.46038333121207198</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.25">
@@ -9519,7 +9485,7 @@
       </c>
       <c r="C33" s="48">
         <f>SUM(C29:C32)</f>
-        <v>1.0000000000000004</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9539,7 +9505,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="43">
-        <v>11.215158746277901</v>
+        <v>10.659739999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9547,7 +9513,7 @@
         <v>45</v>
       </c>
       <c r="C38" s="43">
-        <v>16.079923623550702</v>
+        <v>15.35069</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
@@ -9557,7 +9523,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="43">
-        <v>17.9947473470686</v>
+        <v>17.175809999999998</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
@@ -9567,7 +9533,7 @@
         <v>47</v>
       </c>
       <c r="C40" s="100">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9583,7 +9549,7 @@
         <v>49</v>
       </c>
       <c r="C42" s="43">
-        <v>11.203926129999999</v>
+        <v>10.94176</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9600,7 +9566,7 @@
         <v>51</v>
       </c>
       <c r="C45" s="45">
-        <v>1.15969E-2</v>
+        <v>1.09351E-2</v>
       </c>
       <c r="D45" s="12"/>
     </row>
@@ -9609,7 +9575,7 @@
         <v>52</v>
       </c>
       <c r="C46" s="45">
-        <v>0.1164977</v>
+        <v>0.1174965</v>
       </c>
       <c r="D46" s="12"/>
     </row>
@@ -9618,7 +9584,7 @@
         <v>53</v>
       </c>
       <c r="C47" s="45">
-        <v>5.5259600000000013E-2</v>
+        <v>7.0600399999999994E-2</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
@@ -9628,7 +9594,7 @@
         <v>54</v>
       </c>
       <c r="C48" s="46">
-        <v>0.81664579999999998</v>
+        <v>0.80096800000000001</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -9732,7 +9698,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7fH0Anw4oZ5Uy2FV582AVKmGwt5Jzyrd/LYVcmNkKDK4ZLxJbAVZs56FnD9bQXo8++WsqKRMEBH4bHMv0NO+UA==" saltValue="ReoPnmy3wnkScrVKxH8hSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="50GCOMsu3HEtOqqp+1zrslUIDjwSDUzGYLBQ4p0dPP6GQKe1tcP9o8sbWpBuCdDjVHfbElCqPjWQrWlgfgLV8g==" saltValue="O7f0KFO97s0TSNLDrjglmg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -9764,7 +9730,7 @@
       </c>
       <c r="B1" s="22" t="str">
         <f>"Couverture de l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Couverture de l'année de référence (2021)</v>
+        <v>Couverture de l'année de référence (2024)</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>166</v>
@@ -9787,7 +9753,7 @@
         <v>168</v>
       </c>
       <c r="B2" s="45">
-        <v>0.30019849945160798</v>
+        <v>0</v>
       </c>
       <c r="C2" s="98">
         <v>0.95</v>
@@ -9810,7 +9776,7 @@
         <v>169</v>
       </c>
       <c r="B3" s="45">
-        <v>0</v>
+        <v>0.2066742856206</v>
       </c>
       <c r="C3" s="98">
         <v>0.95</v>
@@ -9862,7 +9828,7 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="56">
-        <v>1.270477719427328</v>
+        <v>1.347849812540453</v>
       </c>
       <c r="E5" s="56" t="s">
         <v>201</v>
@@ -10109,7 +10075,7 @@
         <v>182</v>
       </c>
       <c r="B16" s="45">
-        <v>0.51030420001201693</v>
+        <v>0.95</v>
       </c>
       <c r="C16" s="98">
         <v>0.95</v>
@@ -10132,7 +10098,7 @@
         <v>183</v>
       </c>
       <c r="B17" s="98">
-        <v>0.93</v>
+        <v>0.32122916666666701</v>
       </c>
       <c r="C17" s="98">
         <v>0.95</v>
@@ -10155,7 +10121,7 @@
         <v>157</v>
       </c>
       <c r="B18" s="98">
-        <v>0</v>
+        <v>0.11733278925379</v>
       </c>
       <c r="C18" s="98">
         <v>0.95</v>
@@ -10178,7 +10144,7 @@
         <v>158</v>
       </c>
       <c r="B19" s="98">
-        <v>0</v>
+        <v>0.89972340000000006</v>
       </c>
       <c r="C19" s="98">
         <v>0.95</v>
@@ -10224,7 +10190,7 @@
         <v>184</v>
       </c>
       <c r="B21" s="45">
-        <v>0.12046129999999999</v>
+        <v>0.80314839999999998</v>
       </c>
       <c r="C21" s="98">
         <v>0.95</v>
@@ -10270,7 +10236,7 @@
         <v>186</v>
       </c>
       <c r="B23" s="98">
-        <v>5.8989081380000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C23" s="98">
         <v>0.95</v>
@@ -10293,7 +10259,7 @@
         <v>187</v>
       </c>
       <c r="B24" s="45">
-        <v>0.73019341352905998</v>
+        <v>0.88910919143547995</v>
       </c>
       <c r="C24" s="98">
         <v>0.95</v>
@@ -10362,7 +10328,7 @@
         <v>190</v>
       </c>
       <c r="B27" s="45">
-        <v>0.27909421749389701</v>
+        <v>0</v>
       </c>
       <c r="C27" s="98">
         <v>0.95</v>
@@ -10385,7 +10351,7 @@
         <v>191</v>
       </c>
       <c r="B28" s="45">
-        <v>0.45581739999999998</v>
+        <v>0.69723745018169003</v>
       </c>
       <c r="C28" s="98">
         <v>0.95</v>
@@ -10477,7 +10443,7 @@
         <v>193</v>
       </c>
       <c r="B32" s="45">
-        <v>7.7588900000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="98">
         <v>0.95</v>
@@ -10523,7 +10489,7 @@
         <v>195</v>
       </c>
       <c r="B34" s="45">
-        <v>0.84457583171135597</v>
+        <v>0</v>
       </c>
       <c r="C34" s="98">
         <v>0.95</v>
@@ -10569,7 +10535,7 @@
         <v>197</v>
       </c>
       <c r="B36" s="45">
-        <v>0</v>
+        <v>0.23215369999999999</v>
       </c>
       <c r="C36" s="98">
         <v>0.95</v>
@@ -10615,7 +10581,7 @@
         <v>199</v>
       </c>
       <c r="B38" s="45">
-        <v>0</v>
+        <v>0.45581739999999998</v>
       </c>
       <c r="C38" s="98">
         <v>0.95</v>
@@ -10638,7 +10604,7 @@
         <v>200</v>
       </c>
       <c r="B39" s="45">
-        <v>0.23215369999999999</v>
+        <v>0</v>
       </c>
       <c r="C39" s="98">
         <v>0.95</v>
@@ -10657,7 +10623,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LegWRuhhpAW68u6x5C0sFNKGLBOPYRqGljfF8FjcsSPtp9cf3XXKJq9te+UaLhmylYUjTLD/9iDpWWX7XKzoKA==" saltValue="q0nFfn1BNC439acJka+rag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dNwf6rPlamGoti+/38Ho16IZxYNYV7Gfy0aWC1mKtqnV6cFwQOgCSpgqU6JYBOPebXpaPbJl2O+hh+DKYcS4lA==" saltValue="7370Yk7RULcBv29L4yT3JA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10690,7 +10656,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
         <v>180</v>
       </c>
@@ -10699,7 +10665,7 @@
       </c>
       <c r="C2" s="47"/>
     </row>
-    <row r="3" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="57" t="s">
         <v>181</v>
       </c>
@@ -10708,7 +10674,7 @@
       </c>
       <c r="C3" s="47"/>
     </row>
-    <row r="4" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>192</v>
       </c>
@@ -10717,7 +10683,7 @@
       </c>
       <c r="C4" s="47"/>
     </row>
-    <row r="5" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="57" t="s">
         <v>189</v>
       </c>
@@ -10726,83 +10692,99 @@
       </c>
       <c r="C5" s="47"/>
     </row>
-    <row r="6" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C6" s="58"/>
     </row>
-    <row r="7" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="58"/>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C7" s="58"/>
     </row>
-    <row r="8" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C8" s="58"/>
     </row>
-    <row r="9" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>205</v>
+      </c>
       <c r="C9" s="58"/>
     </row>
-    <row r="10" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
     </row>
-    <row r="11" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="59"/>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
     </row>
-    <row r="12" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="59"/>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
     </row>
-    <row r="13" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="59"/>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
     </row>
-    <row r="14" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="59"/>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
     </row>
-    <row r="15" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="59"/>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
     </row>
-    <row r="16" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="59"/>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
     </row>
-    <row r="17" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="59"/>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
     </row>
-    <row r="18" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
     </row>
-    <row r="19" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
     </row>
-    <row r="20" spans="1:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="psRJ/A2kaOQZVEpewor5nvJLdi6nZQte+B05Lm+rW/YGBdKFKjTnUFhQhz2JHtT9NWym83KqHP1uTbGpZJrDgQ==" saltValue="Eytx9lKFc0qlTW5HMM4GFg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TIf3JuIOaSi5JOgjUDbDDne4hB5c+QaVkwsGZJdZZHEG5mADdbn6j1q7heHmPbN0doVHbol9p8BzF1tCrLD7YQ==" saltValue="KNLqXp06WoSHBA0E2Vygkg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -10827,78 +10809,78 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
     </row>
-    <row r="11" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
     </row>
-    <row r="12" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
     </row>
-    <row r="13" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
     </row>
-    <row r="14" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
     </row>
-    <row r="15" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
     </row>
-    <row r="16" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
     </row>
-    <row r="17" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
     </row>
-    <row r="18" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
     </row>
-    <row r="19" spans="1:1" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LZnPu22euRRx5c7cBzEtBNrQvIsspmN2pJmpmsd4e6iykqVNkkRrXfXzqDfMCdc1NmH9lSrKv56V5ScdRZHoQA==" saltValue="btjQ1g+33GRfwMs4YMq3aA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="J/aL5xLIWYOixWjO3neJdmUsoisAQn0n5TfztuJO8TKeOvluhVObwFc/9cydvtIXCvww7FgeRMsfabDyVanDLw==" saltValue="Flbm+PpOXFHyHkPd41olJQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -10963,23 +10945,23 @@
       </c>
       <c r="B3" s="21">
         <f>frac_mam_1month * 2.6</f>
-        <v>0.10682585940000003</v>
+        <v>0.10682594000000001</v>
       </c>
       <c r="C3" s="21">
         <f>frac_mam_1_5months * 2.6</f>
-        <v>0.10682585940000003</v>
+        <v>0.10682594000000001</v>
       </c>
       <c r="D3" s="21">
         <f>frac_mam_6_11months * 2.6</f>
-        <v>0.2013942346</v>
+        <v>0.20139418000000003</v>
       </c>
       <c r="E3" s="21">
         <f>frac_mam_12_23months * 2.6</f>
-        <v>0.12607114780000001</v>
+        <v>0.12607114</v>
       </c>
       <c r="F3" s="21">
         <f>frac_mam_24_59months * 2.6</f>
-        <v>9.9420970999999997E-2</v>
+        <v>9.9420880000000017E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10988,27 +10970,27 @@
       </c>
       <c r="B4" s="21">
         <f>frac_sam_1month * 2.6</f>
-        <v>6.0566992200000003E-2</v>
+        <v>6.0567000000000003E-2</v>
       </c>
       <c r="C4" s="21">
         <f>frac_sam_1_5months * 2.6</f>
-        <v>6.0566992200000003E-2</v>
+        <v>6.0567000000000003E-2</v>
       </c>
       <c r="D4" s="21">
         <f>frac_sam_6_11months * 2.6</f>
-        <v>1.8212152660000001E-2</v>
+        <v>1.8212220000000001E-2</v>
       </c>
       <c r="E4" s="21">
         <f>frac_sam_12_23months * 2.6</f>
-        <v>4.7944423799999997E-2</v>
+        <v>4.7944520000000004E-2</v>
       </c>
       <c r="F4" s="21">
         <f>frac_sam_24_59months * 2.6</f>
-        <v>1.7275144900000001E-2</v>
+        <v>1.7275180000000001E-2</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ywzb7/9wxkiGfi3i2sOKETUSI1kHw23pqrZk0ABMpv+taaA+1BeM+oRC4AR5n+rlr+7XjVTc91ygv4x0rdw88g==" saltValue="X6fax59pXeMicbZQX9HOXA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="q2VOkBwyNMe7yo05zBo3SG7Q4fJJ4MKf7A6bRfLTN9f4yWP1u3Gx43ohwPgeKrUiwR2BgjYktQptdgK3nF450Q==" saltValue="3FSQw5I3q1e0RTOW2NmN4g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -11461,19 +11443,19 @@
       </c>
       <c r="D10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="E10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="F10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="G10" s="60">
         <f>IF(ISBLANK(comm_deliv), frac_children_health_facility,1)</f>
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="H10" s="61">
         <v>0</v>
@@ -11807,19 +11789,19 @@
       </c>
       <c r="H18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="I18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="J18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="K18" s="60">
         <f>frac_PW_health_facility</f>
-        <v>0.63700000000000001</v>
+        <v>1</v>
       </c>
       <c r="L18" s="61">
         <v>0</v>
@@ -12286,47 +12268,47 @@
       </c>
       <c r="E30" s="60">
         <f t="shared" ref="E30:O30" si="0">frac_maize</f>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="G30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="J30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="M30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="N30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O30" s="60">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12341,47 +12323,47 @@
       </c>
       <c r="E31" s="60">
         <f t="shared" ref="E31:O31" si="1">frac_rice</f>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="J31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="K31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="N31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="O31" s="60">
         <f t="shared" si="1"/>
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12396,47 +12378,47 @@
       </c>
       <c r="E32" s="60">
         <f t="shared" ref="E32:O32" si="2">frac_wheat</f>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="F32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="G32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="H32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="I32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="J32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="K32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="L32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="M32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="N32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
       <c r="O32" s="60">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12764,7 +12746,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="p5DRY3EN7CmcFtj4MQa6RrW1yXWq8FK3gFbMGPrarzJZHodwO0RpeMTuJS/fAdMDdW9dUAW32tro3ZtIWYQalQ==" saltValue="wtg0Z6b1mv7o+W2FmosQ9g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="PmB7aEnmL1IXfedHK2mRnmxDOIyTV2HBsjRr7oegUuS+hB9Efl2oB5YltYv3dQiIfXr1TjoWEQNNODYnz63Ygg==" saltValue="60gnRNFe0At+COkMyMctyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12796,7 +12778,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pcvbF5rrRmi7o6O2BawzGahFtD3fr0C5ZD9ir1iyLWQW+1Hq63mfwzXYnheT0DsTTjG33oLt1EH0itCoYqJk+A==" saltValue="DV6J0p/vuGQUw70TNCaucg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uNxzMQ0tP1OW8TOaMA9ZKvtpFNAUCawJz6lNWxqj/edIsy6gDT8eafrjo3tZszmLU1EW4ieoiAYDidRooXwmHg==" saltValue="GhzWfZvbPU2Vsv761oGHfg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12997,7 +12979,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="80hb2A1pFqDB+yWrtEh75AnVN4cNpvebQs1M14qyu2NE6Hh9ucCxIGsI8uRunk0fL4TpnGEXdC/XG4OPVzIgug==" saltValue="ttKdS3vK+LzgMx/wyiL7dQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uV01jRji9LZa+GrxrKQwLrSCdO0Ok2nCVjjgOBCLOSQcYAuA5sXF29nHmj00cApS1QBf2dfqPBAXKorBgJ7dzQ==" saltValue="AiDKShwd4g5Sj2p0A36V3g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14807,7 +14789,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="M4PB/qigQ22r2o8tArILXz0h7PXsjSnf7ZJpdkHRkfiRPlmZHR37VNrV62z6xJIEiqIFyY0ybtJzv43de3jzDA==" saltValue="3ZL2hdkwUcFhC6366Y+9OA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="J8bq1iRTse3V7YlhlE+kF4nTwk4XDne9NzcOz1UIEevScMb9YF6h9tc9Ud71wZuAkAcdYP+zFv71W6d2PSXTYA==" saltValue="r5OqrAbAOBdwCHmtCXNF8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14869,7 +14851,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>168</v>
       </c>
@@ -14886,7 +14868,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>169</v>
       </c>
@@ -14903,7 +14885,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>170</v>
       </c>
@@ -14920,7 +14902,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>171</v>
       </c>
@@ -14937,7 +14919,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>172</v>
       </c>
@@ -14956,7 +14938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>173</v>
       </c>
@@ -14975,7 +14957,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>174</v>
       </c>
@@ -14994,7 +14976,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>175</v>
       </c>
@@ -15013,7 +14995,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>176</v>
       </c>
@@ -15030,7 +15012,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>177</v>
       </c>
@@ -15047,7 +15029,7 @@
       <c r="J11" s="87"/>
       <c r="K11" s="87"/>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>178</v>
       </c>
@@ -15064,7 +15046,7 @@
       <c r="J12" s="87"/>
       <c r="K12" s="87"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>179</v>
       </c>
@@ -15081,7 +15063,7 @@
       <c r="J13" s="87"/>
       <c r="K13" s="87"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>180</v>
       </c>
@@ -15100,7 +15082,7 @@
       <c r="J14" s="87"/>
       <c r="K14" s="87"/>
     </row>
-    <row r="15" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>181</v>
       </c>
@@ -15119,7 +15101,7 @@
       <c r="J15" s="87"/>
       <c r="K15" s="87"/>
     </row>
-    <row r="16" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>182</v>
       </c>
@@ -15140,7 +15122,7 @@
       <c r="J16" s="87"/>
       <c r="K16" s="87"/>
     </row>
-    <row r="17" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>183</v>
       </c>
@@ -15157,7 +15139,7 @@
       <c r="J17" s="87"/>
       <c r="K17" s="87"/>
     </row>
-    <row r="18" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>157</v>
       </c>
@@ -15176,7 +15158,7 @@
       <c r="J18" s="87"/>
       <c r="K18" s="87"/>
     </row>
-    <row r="19" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>158</v>
       </c>
@@ -15195,7 +15177,7 @@
       <c r="J19" s="87"/>
       <c r="K19" s="87"/>
     </row>
-    <row r="20" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>159</v>
       </c>
@@ -15214,7 +15196,7 @@
       <c r="J20" s="87"/>
       <c r="K20" s="87"/>
     </row>
-    <row r="21" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>184</v>
       </c>
@@ -15233,7 +15215,7 @@
       <c r="J21" s="87"/>
       <c r="K21" s="87"/>
     </row>
-    <row r="22" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>185</v>
       </c>
@@ -15570,7 +15552,7 @@
       <c r="K39" s="87"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="blLrv8Ql7120sJxnoISWKVfEWM5DxwRs1pz5vCYxoib24FVN+Dm/0LjlcUjQGD1+GVU3vEp91asz2qtrfBVnQw==" saltValue="UgxHOZJ49zxl7ZczNrljrA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fdd5uS7w899YwY/oqha5EKcIItU5EelaS9P9DAJXYyh/Wi5AiilSNm639q7lXZlaopIQ/8ovwNje6uVdV5475w==" saltValue="wxXRMvoTtgOoYVKCeAg4XA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15632,7 +15614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>109</v>
       </c>
@@ -15661,7 +15643,7 @@
       <c r="J2" s="87"/>
       <c r="K2" s="87"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>96</v>
       </c>
@@ -15690,7 +15672,7 @@
       <c r="J3" s="87"/>
       <c r="K3" s="87"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>97</v>
       </c>
@@ -15719,7 +15701,7 @@
       <c r="J4" s="87"/>
       <c r="K4" s="87"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>98</v>
       </c>
@@ -15748,7 +15730,7 @@
       <c r="J5" s="87"/>
       <c r="K5" s="87"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>99</v>
       </c>
@@ -15777,7 +15759,7 @@
       <c r="J6" s="87"/>
       <c r="K6" s="87"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>122</v>
       </c>
@@ -15798,7 +15780,7 @@
       <c r="J7" s="87"/>
       <c r="K7" s="87"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>123</v>
       </c>
@@ -15819,7 +15801,7 @@
       <c r="J8" s="87"/>
       <c r="K8" s="87"/>
     </row>
-    <row r="9" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>124</v>
       </c>
@@ -15840,7 +15822,7 @@
       <c r="J9" s="87"/>
       <c r="K9" s="87"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>125</v>
       </c>
@@ -15861,7 +15843,7 @@
       <c r="J10" s="87"/>
       <c r="K10" s="87"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>69</v>
       </c>
@@ -15882,7 +15864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>70</v>
       </c>
@@ -15901,7 +15883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>71</v>
       </c>
@@ -15920,7 +15902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>72</v>
       </c>
@@ -15940,7 +15922,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kx1RT6/vtBHVvUU76A6CIXINtoelujjMreh7EDpPyhIeKD1nNRDZYZcLjypZp39MVM21QUTKMOyuDvFlpeWejQ==" saltValue="DOuROg3/aJqOQAHd0Si8YQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oHmGy0UxUSFaVHuHVm2DARr1VFElI5900nUQ2b4M6FKYXPem7RrCqk6rFXEvKud94ILgCN+DIL3VI3q4w0ORGA==" saltValue="ykKE7C1QSI5F83H4Il1byQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15991,360 +15973,398 @@
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>start_year</f>
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="49">
-        <v>392421.17879999988</v>
+        <v>532402</v>
       </c>
       <c r="C2" s="49">
-        <v>1157000</v>
+        <v>1775399.5</v>
       </c>
       <c r="D2" s="49">
-        <v>1676000</v>
+        <v>2549319</v>
       </c>
       <c r="E2" s="49">
-        <v>732000</v>
+        <v>1464377</v>
       </c>
       <c r="F2" s="49">
-        <v>471000</v>
+        <v>1186209</v>
       </c>
       <c r="G2" s="17">
-        <f t="shared" ref="G2:G11" si="0">C2+D2+E2+F2</f>
-        <v>4036000</v>
+        <f t="shared" ref="G2:G13" si="0">C2+D2+E2+F2</f>
+        <v>6975304.5</v>
       </c>
       <c r="H2" s="17">
-        <f t="shared" ref="H2:H11" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
-        <v>450985.97123465192</v>
+        <f t="shared" ref="H2:H13" si="1">(B2 + stillbirth*B2/(1000-stillbirth))/(1-abortion)</f>
+        <v>611695.29584756587</v>
       </c>
       <c r="I2" s="17">
-        <f t="shared" ref="I2:I11" si="2">G2-H2</f>
-        <v>3585014.0287653483</v>
+        <f t="shared" ref="I2:I13" si="2">G2-H2</f>
+        <v>6363609.2041524341</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A40" si="3">IF($A$2+ROW(A3)-2&lt;=end_year,A2+1,"")</f>
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B3" s="49">
-        <v>409782.53159999999</v>
+        <v>573943</v>
       </c>
       <c r="C3" s="50">
-        <v>1181000</v>
+        <v>1795384.5</v>
       </c>
       <c r="D3" s="50">
-        <v>1816000</v>
+        <v>2780169</v>
       </c>
       <c r="E3" s="50">
-        <v>754000</v>
+        <v>1581613.5</v>
       </c>
       <c r="F3" s="50">
-        <v>485000</v>
+        <v>1231949</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" si="0"/>
-        <v>4236000</v>
+        <v>7389116</v>
       </c>
       <c r="H3" s="17">
         <f t="shared" si="1"/>
-        <v>470938.32594292308</v>
+        <v>659423.20499291795</v>
       </c>
       <c r="I3" s="17">
         <f t="shared" si="2"/>
-        <v>3765061.6740570767</v>
+        <v>6729692.7950070817</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f t="shared" si="3"/>
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="49">
-        <v>429701.86499999987</v>
+        <v>610419</v>
       </c>
       <c r="C4" s="50">
-        <v>1204000</v>
+        <v>1790412</v>
       </c>
       <c r="D4" s="50">
-        <v>1952000</v>
+        <v>2971406.5</v>
       </c>
       <c r="E4" s="50">
-        <v>771000</v>
+        <v>1709798</v>
       </c>
       <c r="F4" s="50">
-        <v>500000</v>
+        <v>1273598.5</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="0"/>
-        <v>4427000</v>
+        <v>7745215</v>
       </c>
       <c r="H4" s="17">
         <f t="shared" si="1"/>
-        <v>493830.41333539336</v>
+        <v>701331.7583254294</v>
       </c>
       <c r="I4" s="17">
         <f t="shared" si="2"/>
-        <v>3933169.5866646068</v>
+        <v>7043883.2416745704</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f t="shared" si="3"/>
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="49">
-        <v>449674.5455999999</v>
+        <v>639263</v>
       </c>
       <c r="C5" s="50">
-        <v>1222000</v>
+        <v>1755175</v>
       </c>
       <c r="D5" s="50">
-        <v>2069000</v>
+        <v>3125682</v>
       </c>
       <c r="E5" s="50">
-        <v>785000</v>
+        <v>1849299.5</v>
       </c>
       <c r="F5" s="50">
-        <v>519000</v>
+        <v>1310525</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="0"/>
-        <v>4595000</v>
+        <v>8040681.5</v>
       </c>
       <c r="H5" s="17">
         <f t="shared" si="1"/>
-        <v>516783.8094443765</v>
+        <v>734471.63968092238</v>
       </c>
       <c r="I5" s="17">
         <f t="shared" si="2"/>
-        <v>4078216.1905556237</v>
+        <v>7306209.860319078</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f t="shared" si="3"/>
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="49">
-        <v>467822.01299999998</v>
+        <v>665188</v>
       </c>
       <c r="C6" s="50">
-        <v>1231000</v>
+        <v>1678421.5</v>
       </c>
       <c r="D6" s="50">
-        <v>2158000</v>
+        <v>3250326.5</v>
       </c>
       <c r="E6" s="50">
-        <v>794000</v>
+        <v>2002848</v>
       </c>
       <c r="F6" s="50">
-        <v>542000</v>
+        <v>1342899</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="0"/>
-        <v>4725000</v>
+        <v>8274495</v>
       </c>
       <c r="H6" s="17">
         <f t="shared" si="1"/>
-        <v>537639.59820650483</v>
+        <v>764257.77974960767</v>
       </c>
       <c r="I6" s="17">
         <f t="shared" si="2"/>
-        <v>4187360.4017934953</v>
+        <v>7510237.2202503923</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f t="shared" si="3"/>
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="49">
-        <v>480535.56400000007</v>
+        <v>684175</v>
       </c>
       <c r="C7" s="50">
-        <v>1244000</v>
+        <v>1574473</v>
       </c>
       <c r="D7" s="50">
-        <v>2241000</v>
+        <v>3335087.5</v>
       </c>
       <c r="E7" s="50">
-        <v>801000</v>
+        <v>2170490.5</v>
       </c>
       <c r="F7" s="50">
-        <v>568000</v>
+        <v>1370461</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="0"/>
-        <v>4854000</v>
+        <v>8450512</v>
       </c>
       <c r="H7" s="17">
         <f t="shared" si="1"/>
-        <v>552250.51488309563</v>
+        <v>786072.60873645917</v>
       </c>
       <c r="I7" s="17">
         <f t="shared" si="2"/>
-        <v>4301749.4851169046</v>
+        <v>7664439.3912635408</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f t="shared" si="3"/>
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="49">
-        <v>490941.87699999998</v>
+        <v>699103</v>
       </c>
       <c r="C8" s="50">
-        <v>1250000</v>
+        <v>1465464.5</v>
       </c>
       <c r="D8" s="50">
-        <v>2302000</v>
+        <v>3371692</v>
       </c>
       <c r="E8" s="50">
-        <v>803000</v>
+        <v>2346187</v>
       </c>
       <c r="F8" s="50">
-        <v>598000</v>
+        <v>1392492.5</v>
       </c>
       <c r="G8" s="17">
         <f t="shared" si="0"/>
-        <v>4953000</v>
+        <v>8575836</v>
       </c>
       <c r="H8" s="17">
         <f t="shared" si="1"/>
-        <v>564209.86220891518</v>
+        <v>803223.91052798601</v>
       </c>
       <c r="I8" s="17">
         <f t="shared" si="2"/>
-        <v>4388790.1377910851</v>
+        <v>7772612.0894720145</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f t="shared" si="3"/>
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="49">
-        <v>499456.12500000012</v>
+        <v>706443</v>
       </c>
       <c r="C9" s="50">
-        <v>1251000</v>
+        <v>1362082.5</v>
       </c>
       <c r="D9" s="50">
-        <v>2347000</v>
+        <v>3363171</v>
       </c>
       <c r="E9" s="50">
-        <v>803000</v>
+        <v>2525926.5</v>
       </c>
       <c r="F9" s="50">
-        <v>630000</v>
+        <v>1410994</v>
       </c>
       <c r="G9" s="17">
         <f t="shared" si="0"/>
-        <v>5031000</v>
+        <v>8662174</v>
       </c>
       <c r="H9" s="17">
         <f t="shared" si="1"/>
-        <v>573994.77344982896</v>
+        <v>811657.09348282288</v>
       </c>
       <c r="I9" s="17">
         <f t="shared" si="2"/>
-        <v>4457005.2265501712</v>
+        <v>7850516.9065171769</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f t="shared" si="3"/>
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="49">
-        <v>506833.04700000008</v>
+        <v>710855</v>
       </c>
       <c r="C10" s="50">
-        <v>1250000</v>
+        <v>1271529</v>
       </c>
       <c r="D10" s="50">
-        <v>2379000</v>
+        <v>3316385.5</v>
       </c>
       <c r="E10" s="50">
-        <v>799000</v>
+        <v>2703312.5</v>
       </c>
       <c r="F10" s="50">
-        <v>661000</v>
+        <v>1428747</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" si="0"/>
-        <v>5089000</v>
+        <v>8719974</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" si="1"/>
-        <v>582472.6245766863</v>
+        <v>816726.19473578501</v>
       </c>
       <c r="I10" s="17">
         <f t="shared" si="2"/>
-        <v>4506527.375423314</v>
+        <v>7903247.805264215</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f t="shared" si="3"/>
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="49">
-        <v>513614.22399999999</v>
+        <v>702271</v>
       </c>
       <c r="C11" s="50">
-        <v>1247000</v>
+        <v>1204044.5</v>
       </c>
       <c r="D11" s="50">
-        <v>2404000</v>
+        <v>3240248</v>
       </c>
       <c r="E11" s="50">
-        <v>795000</v>
+        <v>2868461.5</v>
       </c>
       <c r="F11" s="50">
-        <v>687000</v>
+        <v>1449682.5</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" si="0"/>
-        <v>5133000</v>
+        <v>8762436.5</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" si="1"/>
-        <v>590265.82193879317</v>
+        <v>806863.73663165409</v>
       </c>
       <c r="I11" s="17">
         <f t="shared" si="2"/>
-        <v>4542734.1780612068</v>
+        <v>7955572.7633683458</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
+      <c r="A12" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+        <v>2034</v>
+      </c>
+      <c r="B12" s="49">
+        <v>694568</v>
+      </c>
+      <c r="C12" s="50">
+        <v>1177233</v>
+      </c>
+      <c r="D12" s="50">
+        <v>3131602</v>
+      </c>
+      <c r="E12" s="50">
+        <v>3015146.5</v>
+      </c>
+      <c r="F12" s="50">
+        <v>1480634</v>
+      </c>
+      <c r="G12" s="17">
+        <f t="shared" si="0"/>
+        <v>8804615.5</v>
+      </c>
+      <c r="H12" s="17">
+        <f t="shared" si="1"/>
+        <v>798013.49026910507</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="shared" si="2"/>
+        <v>8006602.009730895</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
+      <c r="A13" s="5">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
+        <v>2035</v>
+      </c>
+      <c r="B13" s="49">
+        <v>680805</v>
+      </c>
+      <c r="C13" s="50">
+        <v>1190252</v>
+      </c>
+      <c r="D13" s="50">
+        <v>2993307</v>
+      </c>
+      <c r="E13" s="50">
+        <v>3139393</v>
+      </c>
+      <c r="F13" s="50">
+        <v>1526329</v>
+      </c>
+      <c r="G13" s="17">
+        <f t="shared" si="0"/>
+        <v>8849281</v>
+      </c>
+      <c r="H13" s="17">
+        <f t="shared" si="1"/>
+        <v>782200.69776128198</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="shared" si="2"/>
+        <v>8067080.3022387177</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
@@ -16751,7 +16771,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qZzEcvAM0WuS4zo48/1s28+MTj8RPTnH8hKz94RNtzhSXHPyf3pNYSDOVgo+8l5C4U0Wox8+kRR1TVO5zAgY1A==" saltValue="R2PJdq23fID3oasEge7/kQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fR+R6b9MgNDJ8GJ1Uyd1xPnN2CLyBZn5MhPjuChRQBblXSuuhMxVHryOkbjXSdluV63vIXjO7d0vdFEO58uIQQ==" saltValue="wdi12HimOCTsTnNscUQV5g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -16830,7 +16850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="104"/>
       <c r="C3" s="8" t="s">
         <v>154</v>
@@ -16852,7 +16872,7 @@
       </c>
       <c r="J3" s="64"/>
     </row>
-    <row r="4" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="104"/>
       <c r="C4" s="8" t="s">
         <v>155</v>
@@ -16874,7 +16894,7 @@
       </c>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="103" t="s">
         <v>109</v>
       </c>
@@ -16882,9 +16902,7 @@
         <v>153</v>
       </c>
       <c r="D5" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.7534066870892262</v>
+        <v>1.73</v>
       </c>
       <c r="E5" s="88">
         <v>1</v>
@@ -16899,15 +16917,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="104"/>
       <c r="C6" s="8" t="s">
         <v>154</v>
       </c>
       <c r="D6" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.56)</f>
-        <v>1.7534066870892262</v>
+        <v>1.73</v>
       </c>
       <c r="E6" s="88">
         <v>1</v>
@@ -16922,7 +16938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="104"/>
       <c r="C7" s="8" t="s">
         <v>155</v>
@@ -16943,7 +16959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="103" t="s">
         <v>96</v>
       </c>
@@ -16954,9 +16970,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>1.6371156384315781</v>
+        <v>1.73</v>
       </c>
       <c r="F8" s="88">
         <v>1</v>
@@ -16968,7 +16982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="104"/>
       <c r="C9" s="8" t="s">
         <v>154</v>
@@ -16977,9 +16991,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="88">
-        <f>IFERROR((MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.56*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.56)</f>
-        <v>1.6371156384315781</v>
+        <v>1.73</v>
       </c>
       <c r="F9" s="88">
         <v>1</v>
@@ -16991,7 +17003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="104"/>
       <c r="C10" s="8" t="s">
         <v>155</v>
@@ -17012,7 +17024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="103" t="s">
         <v>97</v>
       </c>
@@ -17035,7 +17047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="104"/>
       <c r="C12" s="8" t="s">
         <v>154</v>
@@ -17056,7 +17068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="104"/>
       <c r="C13" s="8" t="s">
         <v>155</v>
@@ -17077,7 +17089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="103" t="s">
         <v>98</v>
       </c>
@@ -17100,7 +17112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="104"/>
       <c r="C15" s="8" t="s">
         <v>154</v>
@@ -17121,7 +17133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="104"/>
       <c r="C16" s="8" t="s">
         <v>155</v>
@@ -17165,7 +17177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D18" s="86"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
@@ -17198,7 +17210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20" s="104"/>
       <c r="C20" s="8" t="s">
         <v>154</v>
@@ -17219,7 +17231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="104"/>
       <c r="C21" s="8" t="s">
         <v>155</v>
@@ -17240,7 +17252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>109</v>
       </c>
@@ -17263,7 +17275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23" s="104"/>
       <c r="C23" s="8" t="s">
         <v>154</v>
@@ -17284,7 +17296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24" s="104"/>
       <c r="C24" s="8" t="s">
         <v>155</v>
@@ -17305,7 +17317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>96</v>
       </c>
@@ -17328,7 +17340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" s="104"/>
       <c r="C26" s="8" t="s">
         <v>154</v>
@@ -18010,9 +18022,7 @@
         <v>153</v>
       </c>
       <c r="D58" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.4776928034579877</v>
+        <v>1.35</v>
       </c>
       <c r="E58" s="88">
         <f t="shared" ref="E58:H60" si="1">IF(E5=1,1,E5*0.9)</f>
@@ -18037,9 +18047,7 @@
         <v>154</v>
       </c>
       <c r="D59" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.37)</f>
-        <v>1.4776928034579877</v>
+        <v>1.35</v>
       </c>
       <c r="E59" s="88">
         <f t="shared" si="1"/>
@@ -18096,9 +18104,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>1.4140076896915512</v>
+        <v>1.35</v>
       </c>
       <c r="F61" s="88">
         <f t="shared" ref="F61:H63" si="3">IF(F8=1,1,F8*0.9)</f>
@@ -18123,9 +18129,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="88">
-        <f>IFERROR((MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.37*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.37)</f>
-        <v>1.4140076896915512</v>
+        <v>1.35</v>
       </c>
       <c r="F62" s="88">
         <f t="shared" si="3"/>
@@ -19355,9 +19359,7 @@
         <v>153</v>
       </c>
       <c r="D111" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>2.0864451962149797</v>
+        <v>2.11</v>
       </c>
       <c r="E111" s="88">
         <f t="shared" ref="E111:H113" si="11">IF(E5=1,1,E5*1.05)</f>
@@ -19382,9 +19384,7 @@
         <v>154</v>
       </c>
       <c r="D112" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$C$2))) /
-('Dist. l''allaitement maternel'!$C$2/(1-'Dist. l''allaitement maternel'!$C$2)), 1.77)</f>
-        <v>2.0864451962149797</v>
+        <v>2.11</v>
       </c>
       <c r="E112" s="88">
         <f t="shared" si="11"/>
@@ -19441,9 +19441,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>1.8925801294133848</v>
+        <v>2.11</v>
       </c>
       <c r="F114" s="88">
         <f t="shared" ref="F114:H116" si="13">IF(F8=1,1,F8*1.05)</f>
@@ -19468,9 +19466,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="88">
-        <f>IFERROR((MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2)/(1-MIN(1,1.77*'Dist. l''allaitement maternel'!$D$2))) /
-('Dist. l''allaitement maternel'!$D$2/(1-'Dist. l''allaitement maternel'!$D$2)), 1.77)</f>
-        <v>1.8925801294133848</v>
+        <v>2.11</v>
       </c>
       <c r="F115" s="88">
         <f t="shared" si="13"/>
@@ -20572,7 +20568,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oXjPRJGDc2F6Zvq5VK9XMG62y2E2Pt1fE6dEXdlhV0bafHF174HPc+QogJmljfRsZsuj2wlLWFtpYdxNDxkKPg==" saltValue="nv3dMyxFwNlz41GPSEYRWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="72SrRDbxLPHhjiZOjUbpogtz0RcZp473hLr/sTSapwRXZNp3EN76fWDxOP/e9l9I1Q+TSQwcvGFrdM8Zf8/bRQ==" saltValue="drg0qw1YdDcW4w5iEz7u6g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B148:B150"/>
@@ -21834,7 +21830,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="2EncwRayw6cUbksvjnTSakQStNgZ+NpWRUITHf0q6DWPoT8O3Jl3ZtDbEOroFIXXq3aBXiA36t/gNpzedlBkQw==" saltValue="J81eCKJUxfKDtPnOnSaOEg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NbWg5rI1wLT9d2ZBXg4JM6wNMKBlGHvSfo9ovT7REABsrVehMeBb+nJaBbfg+lx0XGwFSl9U92NETkZbFF+UCw==" saltValue="bLs4tyklFqNY+DJaSgf6Sg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -29969,7 +29965,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yfsBX0eQI4J0FxpUrq28Fh+4STdijujpz1y77PwRyxFtCnlF1bPlahnJkOY5Zyj1LdZsfRnh6EaPEJJUSuSRTw==" saltValue="t7HuCjIi8rLEVDMKn9Uzpg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KRkFCKspo9DpEBFvNghymD4pubE8G0LPbCjm/DXSti2EbzjGpeZRShyYApLc2kTaB9o+Flj3Jri+upKWnGYEQw==" saltValue="XFa54EtUc+uWEXJJ2v10Aw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -30078,13 +30074,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))
-/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.631540860604765</v>
+        <v>0.89</v>
       </c>
       <c r="F6" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.64, (0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.64*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.62105210797667265</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="90">
         <v>1</v>
@@ -30101,12 +30094,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.87608842721526659</v>
+        <v>0.88</v>
       </c>
       <c r="F7" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.87114068985171356</v>
+        <v>0.88</v>
       </c>
       <c r="G7" s="90">
         <v>1</v>
@@ -30123,12 +30114,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$E$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)))/ (SUM('Dist. de l''état nutritionnel'!$E$4:$E$5)/(1-SUM('Dist. de l''état nutritionnel'!$E$4:$E$5))))</f>
-        <v>0.87608842721526659</v>
+        <v>0.88</v>
       </c>
       <c r="F8" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!$F$4),0.88, (0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-0.88*SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)))/ (SUM('Dist. de l''état nutritionnel'!$F$4:$F$5)/(1-SUM('Dist. de l''état nutritionnel'!$F$4:$F$5))))</f>
-        <v>0.87114068985171356</v>
+        <v>0.88</v>
       </c>
       <c r="G8" s="90">
         <v>1</v>
@@ -30406,12 +30395,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.43101936519681283</v>
+        <f>E6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="F29" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.44, (0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.44*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.42006418293097342</v>
+        <f>F6*0.9</f>
+        <v>0.80100000000000005</v>
       </c>
       <c r="G29" s="90">
         <f>IF(G6=1,1,G6*0.9)</f>
@@ -30431,12 +30420,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.84528246268620744</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.83933024390574662</v>
+        <v>0.85</v>
       </c>
       <c r="G30" s="90">
         <f>IF(G7=1,1,G7*0.9)</f>
@@ -30456,12 +30443,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.84528246268620744</v>
+        <v>0.85</v>
       </c>
       <c r="F31" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.85, (0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.85*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.83933024390574662</v>
+        <v>0.85</v>
       </c>
       <c r="G31" s="90">
         <f>IF(G8=1,1,G8*0.9)</f>
@@ -30518,12 +30503,10 @@
         <v>296</v>
       </c>
       <c r="C35" s="90">
-        <f>C12*0.9</f>
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="D35" s="90">
-        <f>D12*0.9</f>
-        <v>1.2509999999999999</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E35" s="90">
         <v>1</v>
@@ -30783,12 +30766,12 @@
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.91726970694548648</v>
+        <f>E6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="F52" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.92, (0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.92*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.91380453856545185</v>
+        <f>F6*1.05</f>
+        <v>0.93450000000000011</v>
       </c>
       <c r="G52" s="90">
         <f>IF(G6=1,1,G6*1.1)</f>
@@ -30808,12 +30791,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.90696293369084025</v>
+        <v>0.91</v>
       </c>
       <c r="F53" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.90311166403137122</v>
+        <v>0.91</v>
       </c>
       <c r="G53" s="90">
         <f>IF(G7=1,1,G7*1.1)</f>
@@ -30833,12 +30814,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!E$4:E$5)))/ (SUM('Dist. de l''état nutritionnel'!E$4:E$5)/(1-SUM('Dist. de l''état nutritionnel'!E$4:E$5))))</f>
-        <v>0.90696293369084025</v>
+        <v>0.91</v>
       </c>
       <c r="F54" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$4),0.91, (0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-0.91*SUM('Dist. de l''état nutritionnel'!F$4:F$5)))/ (SUM('Dist. de l''état nutritionnel'!F$4:F$5)/(1-SUM('Dist. de l''état nutritionnel'!F$4:F$5))))</f>
-        <v>0.90311166403137122</v>
+        <v>0.91</v>
       </c>
       <c r="G54" s="90">
         <f>IF(G8=1,1,G8*1.1)</f>
@@ -30895,12 +30874,10 @@
         <v>309</v>
       </c>
       <c r="C58" s="90">
-        <f>C12*1.1</f>
-        <v>1.6500000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="D58" s="90">
-        <f>D12*1.1</f>
-        <v>1.5289999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="E58" s="90">
         <v>1</v>
@@ -31056,7 +31033,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QN9KsyolHlVOEO50ILK2LGKTVRNW1Ynng75EzXVD/SRCV40lKAKoiixpB77TzfaIr+36FAgujN9jPCzQZhtoTA==" saltValue="rC63/Nh26rLgJv7ArWq+PA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AQfif8E2GKYvuwTmMCRaHbgypmPqe3Wr5daV+d7+WSAW+h5fzpcLBUOye8nIK0OyyVoPV0nYGC1PZ5EjUJbtwQ==" saltValue="Naczhm7Rl0cCMF5ig29W/w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31877,7 +31854,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="r9P1C0s7eB6fTNCmq5w346SswcpQL009JbRUcKzOz8RLGVIo7I46AMd7ILSfTREbtSJEO07hXybFytRD9K9WwA==" saltValue="Yll/NnsDGcWrPSiEX+mpDQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dIGMJEsZOOjBmChzX7pkyIh+Ez7NMRbEeHnNjydgwcarsVm94RjZvDKW6xReQwThUb3OjlPIMxm10ht9Zjz48w==" saltValue="27HaXC4LHTUCdfuGsO3hcg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -31952,7 +31929,7 @@
         <v>171</v>
       </c>
       <c r="C3" s="90">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="D3" s="90">
         <v>0.53</v>
@@ -32287,16 +32264,16 @@
         <v>1</v>
       </c>
       <c r="L10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="M10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="N10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="O10" s="90">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -32463,15 +32440,19 @@
         <v>1</v>
       </c>
       <c r="L14" s="90">
+        <f>L8</f>
         <v>0.51</v>
       </c>
       <c r="M14" s="90">
+        <f>M8</f>
         <v>0.51</v>
       </c>
       <c r="N14" s="90">
+        <f>N8</f>
         <v>0.51</v>
       </c>
       <c r="O14" s="90">
+        <f>O8</f>
         <v>0.51</v>
       </c>
     </row>
@@ -32580,59 +32561,37 @@
         <v>1</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.72,(0.72*'Dist. de l''état nutritionnel'!E$14/(1-0.72*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.57569446104597088</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.72,(0.72*'Dist. de l''état nutritionnel'!F$14/(1-0.72*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.6155480462719104</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.72,(0.72*'Dist. de l''état nutritionnel'!G$14/(1-0.72*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.6155480462719104</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.72,(0.72*'Dist. de l''état nutritionnel'!H$14/(1-0.72*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.64187045942903931</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.72,(0.72*'Dist. de l''état nutritionnel'!I$14/(1-0.72*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.64187045942903931</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.72,(0.72*'Dist. de l''état nutritionnel'!J$14/(1-0.72*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.64187045942903931</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.72,(0.72*'Dist. de l''état nutritionnel'!K$14/(1-0.72*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.64187045942903931</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.72,(0.72*'Dist. de l''état nutritionnel'!L$14/(1-0.72*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.66209692990924884</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.72,(0.72*'Dist. de l''état nutritionnel'!M$14/(1-0.72*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.66209692990924884</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.72,(0.72*'Dist. de l''état nutritionnel'!N$14/(1-0.72*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.66209692990924884</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.72,(0.72*'Dist. de l''état nutritionnel'!O$14/(1-0.72*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.66209692990924884</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -32646,37 +32605,48 @@
         <v>1</v>
       </c>
       <c r="E20" s="90">
-        <v>1</v>
+        <f t="shared" ref="E20:O20" si="0">E19</f>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O20" s="90">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -32690,59 +32660,37 @@
         <v>1</v>
       </c>
       <c r="E21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.8,(0.8*'Dist. de l''état nutritionnel'!E$14/(1-0.8*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.67851506890284685</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.8,(0.8*'Dist. de l''état nutritionnel'!F$14/(1-0.8*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.71351697277203985</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="G21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.8,(0.8*'Dist. de l''état nutritionnel'!G$14/(1-0.8*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.71351697277203985</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.8,(0.8*'Dist. de l''état nutritionnel'!H$14/(1-0.8*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.73600844772967267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.8,(0.8*'Dist. de l''état nutritionnel'!I$14/(1-0.8*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.73600844772967267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.8,(0.8*'Dist. de l''état nutritionnel'!J$14/(1-0.8*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.73600844772967267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="K21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.8,(0.8*'Dist. de l''état nutritionnel'!K$14/(1-0.8*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.73600844772967267</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="L21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.8,(0.8*'Dist. de l''état nutritionnel'!L$14/(1-0.8*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.75296442687747045</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.8,(0.8*'Dist. de l''état nutritionnel'!M$14/(1-0.8*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.75296442687747045</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="N21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.8,(0.8*'Dist. de l''état nutritionnel'!N$14/(1-0.8*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.75296442687747045</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="O21" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.8,(0.8*'Dist. de l''état nutritionnel'!O$14/(1-0.8*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.75296442687747045</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -32803,53 +32751,53 @@
         <v>171</v>
       </c>
       <c r="C26" s="90">
-        <v>0.4</v>
+        <v>0.87</v>
       </c>
       <c r="D26" s="90">
         <v>0.4</v>
       </c>
       <c r="E26" s="90">
-        <f t="shared" ref="E26:O26" si="0">IF(E3=1,1,E3*0.9)</f>
+        <f t="shared" ref="E26:O26" si="1">IF(E3=1,1,E3*0.9)</f>
         <v>1</v>
       </c>
       <c r="F26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O26" s="90">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -32858,23 +32806,23 @@
         <v>176</v>
       </c>
       <c r="C27" s="90">
-        <f t="shared" ref="C27:G33" si="1">IF(C4=1,1,C4*0.9)</f>
+        <f t="shared" ref="C27:G33" si="2">IF(C4=1,1,C4*0.9)</f>
         <v>1</v>
       </c>
       <c r="D27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G27" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H27" s="90">
@@ -32890,19 +32838,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L27" s="90">
-        <f t="shared" ref="L27:O30" si="2">IF(L4=1,1,L4*0.9)</f>
+        <f t="shared" ref="L27:O30" si="3">IF(L4=1,1,L4*0.9)</f>
         <v>1</v>
       </c>
       <c r="M27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O27" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32911,23 +32859,23 @@
         <v>177</v>
       </c>
       <c r="C28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G28" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H28" s="90">
@@ -32943,19 +32891,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O28" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -32964,23 +32912,23 @@
         <v>178</v>
       </c>
       <c r="C29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H29" s="90">
@@ -32996,19 +32944,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O29" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33017,23 +32965,23 @@
         <v>179</v>
       </c>
       <c r="C30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G30" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H30" s="90">
@@ -33049,19 +32997,19 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="L30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="M30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O30" s="90">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -33070,39 +33018,39 @@
         <v>180</v>
       </c>
       <c r="C31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G31" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H31" s="90">
-        <f t="shared" ref="H31:K34" si="3">IF(H8=1,1,H8*0.9)</f>
+        <f t="shared" ref="H31:K34" si="4">IF(H8=1,1,H8*0.9)</f>
         <v>1</v>
       </c>
       <c r="I31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K31" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L31" s="90">
@@ -33123,39 +33071,39 @@
         <v>181</v>
       </c>
       <c r="C32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G32" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K32" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L32" s="90">
@@ -33176,39 +33124,39 @@
         <v>182</v>
       </c>
       <c r="C33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G33" s="90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="H33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K33" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L33" s="90">
@@ -33246,19 +33194,19 @@
         <v>1</v>
       </c>
       <c r="H34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="J34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="K34" s="90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="L34" s="90">
@@ -33327,11 +33275,11 @@
         <v>189</v>
       </c>
       <c r="C36" s="90">
-        <f t="shared" ref="C36:D38" si="4">IF(C13=1,1,C13*0.9)</f>
+        <f t="shared" ref="C36:D38" si="5">IF(C13=1,1,C13*0.9)</f>
         <v>1</v>
       </c>
       <c r="D36" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E36" s="90">
@@ -33344,35 +33292,35 @@
         <v>0.62</v>
       </c>
       <c r="H36" s="90">
-        <f t="shared" ref="H36:O36" si="5">IF(H13=1,1,H13*0.9)</f>
+        <f t="shared" ref="H36:O36" si="6">IF(H13=1,1,H13*0.9)</f>
         <v>1</v>
       </c>
       <c r="I36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="J36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="K36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="L36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="M36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="N36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O36" s="90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -33381,56 +33329,52 @@
         <v>190</v>
       </c>
       <c r="C37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D37" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E37" s="90">
-        <f t="shared" ref="E37:K37" si="6">IF(E14=1,1,E14*0.9)</f>
+        <f t="shared" ref="E37:K37" si="7">IF(E14=1,1,E14*0.9)</f>
         <v>1</v>
       </c>
       <c r="F37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="G37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="H37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="K37" s="90">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <f>L32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="M37" s="90">
-        <f>M32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="N37" s="90">
-        <f>N32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="O37" s="90">
-        <f>O32</f>
-        <v>0.38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -33438,11 +33382,11 @@
         <v>205</v>
       </c>
       <c r="C38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="D38" s="90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="E38" s="90">
@@ -33452,39 +33396,39 @@
         <v>0.3</v>
       </c>
       <c r="G38" s="90">
-        <f t="shared" ref="G38:O38" si="7">IF(G15=1,1,G15*0.9)</f>
+        <f t="shared" ref="G38:O38" si="8">IF(G15=1,1,G15*0.9)</f>
         <v>1</v>
       </c>
       <c r="H38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="J38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="M38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O38" s="90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -33499,55 +33443,55 @@
         <v>173</v>
       </c>
       <c r="C41" s="90">
-        <f t="shared" ref="C41:O41" si="8">IF(C18=1,1,C18*0.9)</f>
+        <f t="shared" ref="C41:O41" si="9">IF(C18=1,1,C18*0.9)</f>
         <v>1</v>
       </c>
       <c r="D41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="E41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="H41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="J41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="L41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="M41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="N41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O41" s="90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -33556,67 +33500,45 @@
         <v>174</v>
       </c>
       <c r="C42" s="90">
-        <f t="shared" ref="C42:D44" si="9">IF(C19=1,1,C19*0.9)</f>
+        <f t="shared" ref="C42:D44" si="10">IF(C19=1,1,C19*0.9)</f>
         <v>1</v>
       </c>
       <c r="D42" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.54,(0.54*'Dist. de l''état nutritionnel'!E$14/(1-0.54*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.38248930529774328</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.54,(0.54*'Dist. de l''état nutritionnel'!F$14/(1-0.54*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.42227901004536011</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.54,(0.54*'Dist. de l''état nutritionnel'!G$14/(1-0.54*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.42227901004536011</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.54,(0.54*'Dist. de l''état nutritionnel'!H$14/(1-0.54*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.45001076065903062</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.54,(0.54*'Dist. de l''état nutritionnel'!I$14/(1-0.54*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.45001076065903062</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.54,(0.54*'Dist. de l''état nutritionnel'!J$14/(1-0.54*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.45001076065903062</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.54,(0.54*'Dist. de l''état nutritionnel'!K$14/(1-0.54*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.45001076065903062</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.54,(0.54*'Dist. de l''état nutritionnel'!L$14/(1-0.54*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.47216229861844222</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.54,(0.54*'Dist. de l''état nutritionnel'!M$14/(1-0.54*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.47216229861844222</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.54,(0.54*'Dist. de l''état nutritionnel'!N$14/(1-0.54*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.47216229861844222</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O42" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.54,(0.54*'Dist. de l''état nutritionnel'!O$14/(1-0.54*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.47216229861844222</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -33624,56 +33546,56 @@
         <v>175</v>
       </c>
       <c r="C43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D43" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E43" s="90">
-        <f t="shared" ref="E43:O43" si="10">IF(E20=1,1,E20*0.9)</f>
-        <v>1</v>
+        <f t="shared" ref="E43:O43" si="11">IF(E20=1,1,E20*0.9)</f>
+        <v>0.87839999999999996</v>
       </c>
       <c r="F43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="G43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="H43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="J43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="K43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="L43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="M43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="N43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
       <c r="O43" s="90">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <f t="shared" si="11"/>
+        <v>0.87839999999999996</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -33681,67 +33603,45 @@
         <v>183</v>
       </c>
       <c r="C44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="D44" s="90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="E44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.7,(0.7*'Dist. de l''état nutritionnel'!E$14/(1-0.7*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.55180331776623381</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.7,(0.7*'Dist. de l''état nutritionnel'!F$14/(1-0.7*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.59231177886371489</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="G44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.7,(0.7*'Dist. de l''état nutritionnel'!G$14/(1-0.7*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.59231177886371489</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.7,(0.7*'Dist. de l''état nutritionnel'!H$14/(1-0.7*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.61924102043406515</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.7,(0.7*'Dist. de l''état nutritionnel'!I$14/(1-0.7*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.61924102043406515</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="J44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.7,(0.7*'Dist. de l''état nutritionnel'!J$14/(1-0.7*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.61924102043406515</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="K44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.7,(0.7*'Dist. de l''état nutritionnel'!K$14/(1-0.7*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.61924102043406515</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="L44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.7,(0.7*'Dist. de l''état nutritionnel'!L$14/(1-0.7*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.64002879769618415</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="M44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.7,(0.7*'Dist. de l''état nutritionnel'!M$14/(1-0.7*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.64002879769618415</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.7,(0.7*'Dist. de l''état nutritionnel'!N$14/(1-0.7*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.64002879769618415</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="O44" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.7,(0.7*'Dist. de l''état nutritionnel'!O$14/(1-0.7*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.64002879769618415</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:15" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -33802,53 +33702,53 @@
         <v>171</v>
       </c>
       <c r="C49" s="90">
-        <v>0.7</v>
+        <v>0.99</v>
       </c>
       <c r="D49" s="90">
         <v>0.7</v>
       </c>
       <c r="E49" s="90">
-        <f t="shared" ref="E49:O49" si="11">IF(E3=1,1,E3*1.05)</f>
+        <f t="shared" ref="E49:O49" si="12">IF(E3=1,1,E3*1.05)</f>
         <v>1</v>
       </c>
       <c r="F49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="G49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="H49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="I49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="J49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="K49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="N49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="O49" s="90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
     </row>
@@ -33857,23 +33757,23 @@
         <v>176</v>
       </c>
       <c r="C50" s="90">
-        <f t="shared" ref="C50:G56" si="12">IF(C4=1,1,C4*1.05)</f>
+        <f t="shared" ref="C50:G56" si="13">IF(C4=1,1,C4*1.05)</f>
         <v>1</v>
       </c>
       <c r="D50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G50" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H50" s="90">
@@ -33889,19 +33789,19 @@
         <v>0.95</v>
       </c>
       <c r="L50" s="90">
-        <f t="shared" ref="L50:O53" si="13">IF(L4=1,1,L4*1.05)</f>
+        <f t="shared" ref="L50:O53" si="14">IF(L4=1,1,L4*1.05)</f>
         <v>1</v>
       </c>
       <c r="M50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O50" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33910,23 +33810,23 @@
         <v>177</v>
       </c>
       <c r="C51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G51" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H51" s="90">
@@ -33942,19 +33842,19 @@
         <v>0.95</v>
       </c>
       <c r="L51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O51" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -33963,23 +33863,23 @@
         <v>178</v>
       </c>
       <c r="C52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G52" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H52" s="90">
@@ -33995,19 +33895,19 @@
         <v>0.95</v>
       </c>
       <c r="L52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O52" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34016,23 +33916,23 @@
         <v>179</v>
       </c>
       <c r="C53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G53" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H53" s="90">
@@ -34048,19 +33948,19 @@
         <v>0.95</v>
       </c>
       <c r="L53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="M53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="N53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="O53" s="90">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
     </row>
@@ -34069,39 +33969,39 @@
         <v>180</v>
       </c>
       <c r="C54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G54" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H54" s="90">
-        <f t="shared" ref="H54:K57" si="14">IF(H8=1,1,H8*1.05)</f>
+        <f t="shared" ref="H54:K57" si="15">IF(H8=1,1,H8*1.05)</f>
         <v>1</v>
       </c>
       <c r="I54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K54" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L54" s="90">
@@ -34122,39 +34022,39 @@
         <v>181</v>
       </c>
       <c r="C55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G55" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K55" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L55" s="90">
@@ -34175,52 +34075,52 @@
         <v>182</v>
       </c>
       <c r="C56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="D56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="E56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="F56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="G56" s="90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="H56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K56" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="M56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="N56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O56" s="90">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -34246,19 +34146,19 @@
         <v>1</v>
       </c>
       <c r="H57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="I57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="J57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="K57" s="90">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="L57" s="90">
@@ -34327,11 +34227,11 @@
         <v>189</v>
       </c>
       <c r="C59" s="90">
-        <f t="shared" ref="C59:D61" si="15">IF(C13=1,1,C13*1.05)</f>
+        <f t="shared" ref="C59:D61" si="16">IF(C13=1,1,C13*1.05)</f>
         <v>1</v>
       </c>
       <c r="D59" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E59" s="90">
@@ -34344,35 +34244,35 @@
         <v>0.77</v>
       </c>
       <c r="H59" s="90">
-        <f t="shared" ref="H59:O59" si="16">IF(H13=1,1,H13*1.05)</f>
+        <f t="shared" ref="H59:O59" si="17">IF(H13=1,1,H13*1.05)</f>
         <v>1</v>
       </c>
       <c r="I59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O59" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34381,56 +34281,52 @@
         <v>190</v>
       </c>
       <c r="C60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D60" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E60" s="90">
-        <f t="shared" ref="E60:K60" si="17">IF(E14=1,1,E14*1.05)</f>
+        <f t="shared" ref="E60:K60" si="18">IF(E14=1,1,E14*1.05)</f>
         <v>1</v>
       </c>
       <c r="F60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="H60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="I60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="J60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="K60" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <f>L54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="M60" s="90">
-        <f>M54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N60" s="90">
-        <f>N54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O60" s="90">
-        <f>O54</f>
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34438,11 +34334,11 @@
         <v>205</v>
       </c>
       <c r="C61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="D61" s="90">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="E61" s="90">
@@ -34452,39 +34348,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="18">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="19">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
@@ -34499,55 +34395,55 @@
         <v>173</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:O64" si="19">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:O64" si="20">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="F64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="J64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="K64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="N64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="O64" s="90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -34556,67 +34452,45 @@
         <v>174</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" ref="C65:D67" si="20">IF(C19=1,1,C19*1.05)</f>
+        <f t="shared" ref="C65:D67" si="21">IF(C19=1,1,C19*1.05)</f>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.97,(0.97*'Dist. de l''état nutritionnel'!E$14/(1-0.97*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.94463025939272638</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.97,(0.97*'Dist. de l''état nutritionnel'!F$14/(1-0.97*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.95267933434885588</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.97,(0.97*'Dist. de l''état nutritionnel'!G$14/(1-0.97*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.95267933434885588</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.97,(0.97*'Dist. de l''état nutritionnel'!H$14/(1-0.97*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.95751249840671881</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.97,(0.97*'Dist. de l''état nutritionnel'!I$14/(1-0.97*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.95751249840671881</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.97,(0.97*'Dist. de l''état nutritionnel'!J$14/(1-0.97*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.95751249840671881</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.97,(0.97*'Dist. de l''état nutritionnel'!K$14/(1-0.97*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.95751249840671881</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.97,(0.97*'Dist. de l''état nutritionnel'!L$14/(1-0.97*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.96099539745689988</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.97,(0.97*'Dist. de l''état nutritionnel'!M$14/(1-0.97*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.96099539745689988</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.97,(0.97*'Dist. de l''état nutritionnel'!N$14/(1-0.97*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.96099539745689988</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O65" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.97,(0.97*'Dist. de l''état nutritionnel'!O$14/(1-0.97*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.96099539745689988</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
@@ -34624,56 +34498,56 @@
         <v>175</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
-        <f t="shared" ref="E66:O66" si="21">IF(E20=1,1,E20*1.05)</f>
-        <v>1</v>
+        <f t="shared" ref="E66:O66" si="22">IF(E20=1,1,E20*1.05)</f>
+        <v>1.0247999999999999</v>
       </c>
       <c r="F66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="G66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="H66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="I66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="J66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="K66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="L66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="M66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="N66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
       <c r="O66" s="90">
-        <f t="shared" si="21"/>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>1.0247999999999999</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
@@ -34681,71 +34555,49 @@
         <v>183</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$14),0.92,(0.92*'Dist. de l''état nutritionnel'!E$14/(1-0.92*'Dist. de l''état nutritionnel'!E$14))
-/ ('Dist. de l''état nutritionnel'!E$14/(1-'Dist. de l''état nutritionnel'!E$14)))</f>
-        <v>0.85851478650126933</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$14),0.92,(0.92*'Dist. de l''état nutritionnel'!F$14/(1-0.92*'Dist. de l''état nutritionnel'!F$14))
-/ ('Dist. de l''état nutritionnel'!F$14/(1-'Dist. de l''état nutritionnel'!F$14)))</f>
-        <v>0.87745846706156283</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="G67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$14),0.92,(0.92*'Dist. de l''état nutritionnel'!G$14/(1-0.92*'Dist. de l''état nutritionnel'!G$14))
-/ ('Dist. de l''état nutritionnel'!G$14/(1-'Dist. de l''état nutritionnel'!G$14)))</f>
-        <v>0.87745846706156283</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!H$14),0.92,(0.92*'Dist. de l''état nutritionnel'!H$14/(1-0.92*'Dist. de l''état nutritionnel'!H$14))
-/ ('Dist. de l''état nutritionnel'!H$14/(1-'Dist. de l''état nutritionnel'!H$14)))</f>
-        <v>0.88907991791913932</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="I67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!I$14),0.92,(0.92*'Dist. de l''état nutritionnel'!I$14/(1-0.92*'Dist. de l''état nutritionnel'!I$14))
-/ ('Dist. de l''état nutritionnel'!I$14/(1-'Dist. de l''état nutritionnel'!I$14)))</f>
-        <v>0.88907991791913932</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!J$14),0.92,(0.92*'Dist. de l''état nutritionnel'!J$14/(1-0.92*'Dist. de l''état nutritionnel'!J$14))
-/ ('Dist. de l''état nutritionnel'!J$14/(1-'Dist. de l''état nutritionnel'!J$14)))</f>
-        <v>0.88907991791913932</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="K67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!K$14),0.92,(0.92*'Dist. de l''état nutritionnel'!K$14/(1-0.92*'Dist. de l''état nutritionnel'!K$14))
-/ ('Dist. de l''état nutritionnel'!K$14/(1-'Dist. de l''état nutritionnel'!K$14)))</f>
-        <v>0.88907991791913932</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="L67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!L$14),0.92,(0.92*'Dist. de l''état nutritionnel'!L$14/(1-0.92*'Dist. de l''état nutritionnel'!L$14))
-/ ('Dist. de l''état nutritionnel'!L$14/(1-'Dist. de l''état nutritionnel'!L$14)))</f>
-        <v>0.89757246747925845</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="M67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!M$14),0.92,(0.92*'Dist. de l''état nutritionnel'!M$14/(1-0.92*'Dist. de l''état nutritionnel'!M$14))
-/ ('Dist. de l''état nutritionnel'!M$14/(1-'Dist. de l''état nutritionnel'!M$14)))</f>
-        <v>0.89757246747925845</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="N67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!N$14),0.92,(0.92*'Dist. de l''état nutritionnel'!N$14/(1-0.92*'Dist. de l''état nutritionnel'!N$14))
-/ ('Dist. de l''état nutritionnel'!N$14/(1-'Dist. de l''état nutritionnel'!N$14)))</f>
-        <v>0.89757246747925845</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="O67" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!O$14),0.92,(0.92*'Dist. de l''état nutritionnel'!O$14/(1-0.92*'Dist. de l''état nutritionnel'!O$14))
-/ ('Dist. de l''état nutritionnel'!O$14/(1-'Dist. de l''état nutritionnel'!O$14)))</f>
-        <v>0.89757246747925845</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="N+qSzqZRywaFjvVs+882Z6z/B63ew7lHj2zQTkXuQYjTdrp3CyhhgIZCJ7KESaFDbTZ4VvUGw51skRdFzMOnjw==" saltValue="Dp945ULdWYq1X5e4vBRh1g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5kfPfT3ghkfrT1Cppoamn3+wYpbCQzd1NbUc1shOV8TubxwWQJr7KYwnWxR3jXtKLJzoYKNJMhx99cLQ+6ONfw==" saltValue="azPOeemq+pyhvMcRchsPzw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -34791,7 +34643,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>161</v>
       </c>
@@ -34799,24 +34651,20 @@
         <v>1</v>
       </c>
       <c r="D3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.74745638897657141</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.75056601218488095</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.74839119749593253</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G3" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.75063394019192409</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34830,7 +34678,7 @@
       <c r="F4" s="83"/>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>165</v>
       </c>
@@ -34838,24 +34686,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.74397033278420366</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="E5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.73653550297187587</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="F5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.74249150025112898</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
       <c r="G5" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.33),((1/1.33)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.33)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.74453481886490991</v>
+        <f>1/1.33</f>
+        <v>0.75187969924812026</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34887,7 +34731,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>161</v>
       </c>
@@ -34895,24 +34739,20 @@
         <v>1</v>
       </c>
       <c r="D10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.64396504334600668</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.64774843675209925</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.64510104245082034</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G10" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.64783122712771635</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34926,7 +34766,7 @@
       <c r="F11" s="83"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>165</v>
       </c>
@@ -34934,24 +34774,20 @@
         <v>1</v>
       </c>
       <c r="D12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.63973896229747551</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="E12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.63077950052697296</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="F12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.6379510678223268</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
       <c r="G12" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.54),((1/1.54)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.54)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.64042218390964989</v>
+        <f>1/1.54</f>
+        <v>0.64935064935064934</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="92" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -34983,7 +34819,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
         <v>161</v>
       </c>
@@ -34991,24 +34827,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$11))
-/ ('Dist. de l''état nutritionnel'!D$11/(1-'Dist. de l''état nutritionnel'!D$11)))</f>
-        <v>0.85924228398948999</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$11))
-/ ('Dist. de l''état nutritionnel'!E$11/(1-'Dist. de l''état nutritionnel'!E$11)))</f>
-        <v>0.86123100726786728</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$11))
-/ ('Dist. de l''état nutritionnel'!F$11/(1-'Dist. de l''état nutritionnel'!F$11)))</f>
-        <v>0.85984089943066222</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G17" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$11),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$11/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$11))
-/ ('Dist. de l''état nutritionnel'!G$11/(1-'Dist. de l''état nutritionnel'!G$11)))</f>
-        <v>0.86127436823938708</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.3">
@@ -35022,7 +34854,7 @@
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>165</v>
       </c>
@@ -35030,28 +34862,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!D$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!D$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!D$10))
-/ ('Dist. de l''état nutritionnel'!D$10/(1-'Dist. de l''état nutritionnel'!D$10)))</f>
-        <v>0.85700409123181531</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="E19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!E$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!E$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!E$10))
-/ ('Dist. de l''état nutritionnel'!E$10/(1-'Dist. de l''état nutritionnel'!E$10)))</f>
-        <v>0.85219954953766697</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="F19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!F$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!F$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!F$10))
-/ ('Dist. de l''état nutritionnel'!F$10/(1-'Dist. de l''état nutritionnel'!F$10)))</f>
-        <v>0.85605181951683218</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
       <c r="G19" s="90">
-        <f>IF(ISBLANK('Dist. de l''état nutritionnel'!G$10),(1/1.16),((1/1.16)*'Dist. de l''état nutritionnel'!G$10/(1-(1/1.16)*'Dist. de l''état nutritionnel'!G$10))
-/ ('Dist. de l''état nutritionnel'!G$10/(1-'Dist. de l''état nutritionnel'!G$10)))</f>
-        <v>0.85736714285344351</v>
+        <f>1/1.16</f>
+        <v>0.86206896551724144</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mJ1OVo1X6o7ykTE3zF/hXhV22eGsM2f/KIRSlCNKtj4fjtXwa4w1jmA7XHW3F7ylYcl7UbGw7paTIFuiPm7bmQ==" saltValue="aM1LW4NsBTiwSZUtlp2E3g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="m/gEanPxz48S5ASOznPg1tSo8tj3z+cm2p3ZwLtliSoDngWDy7pMY6OGNhivJ43PdNi/SYa465zf48/5U1pLGw==" saltValue="IzlPkg6hVW8AR6Rd1xM6dg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -35104,7 +34932,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>193</v>
       </c>
@@ -35130,7 +34958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
         <v>335</v>
       </c>
@@ -35150,7 +34978,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
         <v>336</v>
       </c>
@@ -35170,7 +34998,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>192</v>
       </c>
@@ -35196,7 +35024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C6" s="5" t="s">
         <v>336</v>
       </c>
@@ -35216,7 +35044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>209</v>
       </c>
@@ -35239,7 +35067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>336</v>
       </c>
@@ -35259,7 +35087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>185</v>
       </c>
@@ -35285,7 +35113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>336</v>
       </c>
@@ -35305,7 +35133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>209</v>
       </c>
@@ -35328,7 +35156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>336</v>
       </c>
@@ -35348,7 +35176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>205</v>
       </c>
@@ -35374,7 +35202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>336</v>
       </c>
@@ -35394,7 +35222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>209</v>
       </c>
@@ -35417,7 +35245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>336</v>
       </c>
@@ -35437,7 +35265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>170</v>
       </c>
@@ -35463,7 +35291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C18" s="5" t="s">
         <v>336</v>
       </c>
@@ -35483,7 +35311,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>209</v>
       </c>
@@ -35506,7 +35334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
         <v>336</v>
       </c>
@@ -35526,7 +35354,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>175</v>
       </c>
@@ -35552,7 +35380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>335</v>
       </c>
@@ -35572,7 +35400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>173</v>
       </c>
@@ -35598,7 +35426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C24" s="5" t="s">
         <v>335</v>
       </c>
@@ -35618,7 +35446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>174</v>
       </c>
@@ -35644,7 +35472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
         <v>335</v>
       </c>
@@ -35664,7 +35492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>197</v>
       </c>
@@ -35690,7 +35518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>335</v>
       </c>
@@ -35710,7 +35538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>336</v>
       </c>
@@ -35730,7 +35558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>198</v>
       </c>
@@ -35756,7 +35584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C31" s="5" t="s">
         <v>335</v>
       </c>
@@ -35776,7 +35604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
         <v>336</v>
       </c>
@@ -35796,7 +35624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>196</v>
       </c>
@@ -35822,7 +35650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>335</v>
       </c>
@@ -35842,7 +35670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C35" s="5" t="s">
         <v>336</v>
       </c>
@@ -35862,7 +35690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>195</v>
       </c>
@@ -35888,7 +35716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
         <v>335</v>
       </c>
@@ -35908,7 +35736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" s="5" t="s">
         <v>336</v>
       </c>
@@ -35928,7 +35756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>194</v>
       </c>
@@ -35954,7 +35782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>335</v>
       </c>
@@ -35974,7 +35802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C41" s="5" t="s">
         <v>336</v>
       </c>
@@ -35994,7 +35822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>200</v>
       </c>
@@ -36020,7 +35848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
         <v>335</v>
       </c>
@@ -36040,7 +35868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>336</v>
       </c>
@@ -36060,7 +35888,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
         <v>88</v>
       </c>
@@ -36083,7 +35911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>335</v>
       </c>
@@ -36103,7 +35931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C47" s="5" t="s">
         <v>336</v>
       </c>
@@ -36123,7 +35951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>191</v>
       </c>
@@ -36149,7 +35977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C49" s="5" t="s">
         <v>335</v>
       </c>
@@ -36169,7 +35997,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>199</v>
       </c>
@@ -36195,7 +36023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C51" s="5" t="s">
         <v>335</v>
       </c>
@@ -36215,7 +36043,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>184</v>
       </c>
@@ -36241,12 +36069,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C53" s="5" t="s">
         <v>335</v>
       </c>
       <c r="D53" s="90">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="E53" s="90">
         <v>0</v>
@@ -36294,7 +36122,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>193</v>
       </c>
@@ -36325,7 +36153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C58" s="5" t="s">
         <v>335</v>
       </c>
@@ -36347,7 +36175,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C59" s="5" t="s">
         <v>336</v>
       </c>
@@ -36369,7 +36197,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>192</v>
       </c>
@@ -36395,7 +36223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C61" s="5" t="s">
         <v>336</v>
       </c>
@@ -36415,7 +36243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
         <v>209</v>
       </c>
@@ -36438,7 +36266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" s="5" t="s">
         <v>336</v>
       </c>
@@ -36458,7 +36286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>185</v>
       </c>
@@ -36484,7 +36312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C65" s="5" t="s">
         <v>336</v>
       </c>
@@ -36504,7 +36332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
         <v>209</v>
       </c>
@@ -36527,7 +36355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C67" s="5" t="s">
         <v>336</v>
       </c>
@@ -36547,7 +36375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>205</v>
       </c>
@@ -36573,7 +36401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C69" s="5" t="s">
         <v>336</v>
       </c>
@@ -36596,7 +36424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="5" t="s">
         <v>209</v>
       </c>
@@ -36624,7 +36452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C71" s="5" t="s">
         <v>336</v>
       </c>
@@ -36647,7 +36475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>170</v>
       </c>
@@ -36678,7 +36506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" s="5" t="s">
         <v>336</v>
       </c>
@@ -37502,7 +37330,7 @@
         <v>335</v>
       </c>
       <c r="D108" s="90">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E108" s="90">
         <v>0</v>
@@ -38763,7 +38591,7 @@
         <v>335</v>
       </c>
       <c r="D163" s="90">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="E163" s="90">
         <v>0</v>
@@ -38779,7 +38607,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LT/CTSHJwkunsfOZ2h/RNEVm7si2BeAo9ocKTGHMJs7kTwNPFuANwaSaLdIDC365y7XeuwwcuUgn/bTf8F72xg==" saltValue="QzrDK3WZOPfpqFrQlBal5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xipDdydboIKu1+QsZcy70A8Yqw1W0U0CiZYbQKR8bYfVHsSkD+SGWwbIYJJF6Ab41XPdtS0PS/vgN51GNldywg==" saltValue="O/CrMfeksbqMdne35BBN8g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -38824,7 +38652,7 @@
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>169</v>
       </c>
@@ -38848,7 +38676,7 @@
       </c>
       <c r="H2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C3" s="8" t="s">
         <v>335</v>
       </c>
@@ -38866,7 +38694,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>188</v>
       </c>
@@ -38890,7 +38718,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C5" s="8" t="s">
         <v>335</v>
       </c>
@@ -38908,7 +38736,7 @@
       </c>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>187</v>
       </c>
@@ -38932,7 +38760,7 @@
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C7" s="8" t="s">
         <v>335</v>
       </c>
@@ -38976,7 +38804,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>169</v>
       </c>
@@ -39003,7 +38831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C12" s="8" t="s">
         <v>335</v>
       </c>
@@ -39020,7 +38848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>188</v>
       </c>
@@ -39047,7 +38875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C14" s="8" t="s">
         <v>335</v>
       </c>
@@ -39068,7 +38896,7 @@
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>187</v>
       </c>
@@ -39095,7 +38923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C16" s="8" t="s">
         <v>335</v>
       </c>
@@ -39142,7 +38970,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>169</v>
       </c>
@@ -39169,7 +38997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C21" s="8" t="s">
         <v>335</v>
       </c>
@@ -39186,7 +39014,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>188</v>
       </c>
@@ -39213,7 +39041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C23" s="8" t="s">
         <v>335</v>
       </c>
@@ -39234,7 +39062,7 @@
         <v>0.64900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>187</v>
       </c>
@@ -39261,7 +39089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C25" s="8" t="s">
         <v>335</v>
       </c>
@@ -39283,7 +39111,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VbyR7hfobStVqG60y/nzjR8D2yd2z8ToK58Y8PtEVOV/462pLIcvLjuMVHoB3jJqYjNm6/9+OlbXYwrtybQzAw==" saltValue="a95H1c1Zw12mOLK7ZmKVxg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="U/vwDYWUjhWXXMjWI5nCKe5kidfXZEZjNcqqfXQpRL4DvxBdNeLmr75kygezWORrZP3Tc/0WsmQlhG8j6flsVg==" saltValue="EMOw+47VM8pOpWN398E7HQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -39305,7 +39133,7 @@
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="str">
         <f>"Pourcentage des morts de l'année de référence ("&amp;start_year&amp;") imputable à chaque cause"</f>
-        <v>Pourcentage des morts de l'année de référence (2021) imputable à chaque cause</v>
+        <v>Pourcentage des morts de l'année de référence (2024) imputable à chaque cause</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -39341,7 +39169,7 @@
         <v>79</v>
       </c>
       <c r="C4" s="101">
-        <v>0.15674200299506441</v>
+        <v>0.15451909999999969</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39349,7 +39177,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="101">
-        <v>2.5581404940566779E-3</v>
+        <v>4.2198999999999926E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39357,7 +39185,7 @@
         <v>81</v>
       </c>
       <c r="C6" s="101">
-        <v>0.18902452665792679</v>
+        <v>0.19492200000000021</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39365,7 +39193,7 @@
         <v>82</v>
       </c>
       <c r="C7" s="101">
-        <v>0.43305943212979531</v>
+        <v>0.42669009999999979</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39381,7 +39209,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="101">
-        <v>0.1610509257617517</v>
+        <v>0.16146820000000039</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39389,7 +39217,7 @@
         <v>85</v>
       </c>
       <c r="C10" s="101">
-        <v>5.7564971961404997E-2</v>
+        <v>5.8180699999999898E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39438,16 +39266,16 @@
         <v>87</v>
       </c>
       <c r="C14" s="55">
-        <v>3.4332729109268191E-2</v>
+        <v>6.2116492322683313E-2</v>
       </c>
       <c r="D14" s="55">
-        <v>3.4332729109268191E-2</v>
+        <v>6.2116492322683313E-2</v>
       </c>
       <c r="E14" s="55">
-        <v>3.4332729109268191E-2</v>
+        <v>6.2116492322683313E-2</v>
       </c>
       <c r="F14" s="55">
-        <v>3.4332729109268191E-2</v>
+        <v>6.2116492322683313E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39455,16 +39283,16 @@
         <v>88</v>
       </c>
       <c r="C15" s="101">
-        <v>0.1407154435741641</v>
+        <v>0.29688997844133608</v>
       </c>
       <c r="D15" s="101">
-        <v>0.1407154435741641</v>
+        <v>0.29688997844133608</v>
       </c>
       <c r="E15" s="101">
-        <v>0.1407154435741641</v>
+        <v>0.29688997844133608</v>
       </c>
       <c r="F15" s="101">
-        <v>0.1407154435741641</v>
+        <v>0.29688997844133608</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39472,16 +39300,16 @@
         <v>89</v>
       </c>
       <c r="C16" s="101">
-        <v>3.1107140261866659E-2</v>
+        <v>5.627712966098989E-2</v>
       </c>
       <c r="D16" s="101">
-        <v>3.1107140261866659E-2</v>
+        <v>5.627712966098989E-2</v>
       </c>
       <c r="E16" s="101">
-        <v>3.1107140261866659E-2</v>
+        <v>5.627712966098989E-2</v>
       </c>
       <c r="F16" s="101">
-        <v>3.1107140261866659E-2</v>
+        <v>5.627712966098989E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39540,16 +39368,16 @@
         <v>93</v>
       </c>
       <c r="C20" s="101">
-        <v>4.2673061915751313E-2</v>
+        <v>6.7017783841196291E-2</v>
       </c>
       <c r="D20" s="101">
-        <v>4.2673061915751313E-2</v>
+        <v>6.7017783841196291E-2</v>
       </c>
       <c r="E20" s="101">
-        <v>4.2673061915751313E-2</v>
+        <v>6.7017783841196291E-2</v>
       </c>
       <c r="F20" s="101">
-        <v>4.2673061915751313E-2</v>
+        <v>6.7017783841196291E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39557,16 +39385,16 @@
         <v>94</v>
       </c>
       <c r="C21" s="101">
-        <v>0.21286174796692209</v>
+        <v>0.38511254926272848</v>
       </c>
       <c r="D21" s="101">
-        <v>0.21286174796692209</v>
+        <v>0.38511254926272848</v>
       </c>
       <c r="E21" s="101">
-        <v>0.21286174796692209</v>
+        <v>0.38511254926272848</v>
       </c>
       <c r="F21" s="101">
-        <v>0.21286174796692209</v>
+        <v>0.38511254926272848</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39574,16 +39402,16 @@
         <v>95</v>
       </c>
       <c r="C22" s="101">
-        <v>0.53830987717202761</v>
+        <v>0.13258606647106591</v>
       </c>
       <c r="D22" s="101">
-        <v>0.53830987717202761</v>
+        <v>0.13258606647106591</v>
       </c>
       <c r="E22" s="101">
-        <v>0.53830987717202761</v>
+        <v>0.13258606647106591</v>
       </c>
       <c r="F22" s="101">
-        <v>0.53830987717202761</v>
+        <v>0.13258606647106591</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39716,7 +39544,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oCsI1/bMe0NzHnWPncHEcnLkYVtg0WMUAp91NslJHJuQDudC+a6iGLctjZ68NCZiWUiW6AONZT4zltvPY0zh3w==" saltValue="gCWtzXfekAOSCSOT/r5P8w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/0NquUf1PPvsxRgqXrhWAqOq5+M+cctSX/I+H7B25dZL3w420M9tNRC7nDSJqRloVNarezotpPmUqrWs2m5v1w==" saltValue="+B1f2S8GJuheiJYulzcO3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39738,7 +39566,7 @@
     <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Pourcentage de la population dans chaque catégorie pendant l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Pourcentage de la population dans chaque catégorie pendant l'année de référence (2021)</v>
+        <v>Pourcentage de la population dans chaque catégorie pendant l'année de référence (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>110</v>
@@ -39768,23 +39596,23 @@
       </c>
       <c r="C2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.71787305407374347</v>
+        <v>0.71787283692135273</v>
       </c>
       <c r="D2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.71787305407374347</v>
+        <v>0.71787283692135273</v>
       </c>
       <c r="E2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.78835828140046849</v>
+        <v>0.78835830343249902</v>
       </c>
       <c r="F2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.66194714301183777</v>
+        <v>0.66194727070227766</v>
       </c>
       <c r="G2" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.61735892155936034</v>
+        <v>0.61735896378344113</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39793,23 +39621,23 @@
       </c>
       <c r="C3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C4:C5), 0, 1) + 1, 0, 1, TRUE) - SUM(C4:C5), "")</f>
-        <v>0.22467561992625654</v>
+        <v>0.22467576307864728</v>
       </c>
       <c r="D3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D4:D5), 0, 1) + 1, 0, 1, TRUE) - SUM(D4:D5), "")</f>
-        <v>0.22467561992625654</v>
+        <v>0.22467576307864728</v>
       </c>
       <c r="E3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E4:E5), 0, 1) + 1, 0, 1, TRUE) - SUM(E4:E5), "")</f>
-        <v>0.17576961259953156</v>
+        <v>0.17576959656750102</v>
       </c>
       <c r="F3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F4:F5), 0, 1) + 1, 0, 1, TRUE) - SUM(F4:F5), "")</f>
-        <v>0.25992580598816228</v>
+        <v>0.25992572929772234</v>
       </c>
       <c r="G3" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G4:G5), 0, 1) + 1, 0, 1, TRUE) - SUM(G4:G5), "")</f>
-        <v>0.28559215944063965</v>
+        <v>0.28559213621655893</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39817,19 +39645,19 @@
         <v>114</v>
       </c>
       <c r="C4" s="45">
-        <v>4.5964250999999998E-2</v>
+        <v>4.59643E-2</v>
       </c>
       <c r="D4" s="53">
-        <v>4.5964250999999998E-2</v>
+        <v>4.59643E-2</v>
       </c>
       <c r="E4" s="53">
-        <v>1.7641047999999999E-2</v>
+        <v>1.7641E-2</v>
       </c>
       <c r="F4" s="53">
-        <v>6.0780543999999999E-2</v>
+        <v>6.0780500000000001E-2</v>
       </c>
       <c r="G4" s="53">
-        <v>7.2927145999999998E-2</v>
+        <v>7.2927099999999995E-2</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39837,19 +39665,19 @@
         <v>115</v>
       </c>
       <c r="C5" s="45">
-        <v>1.1487074999999999E-2</v>
+        <v>1.14871E-2</v>
       </c>
       <c r="D5" s="53">
-        <v>1.1487074999999999E-2</v>
+        <v>1.14871E-2</v>
       </c>
       <c r="E5" s="53">
-        <v>1.8231058000000001E-2</v>
+        <v>1.82311E-2</v>
       </c>
       <c r="F5" s="53">
-        <v>1.7346507000000001E-2</v>
+        <v>1.7346500000000001E-2</v>
       </c>
       <c r="G5" s="53">
-        <v>2.4121772999999999E-2</v>
+        <v>2.4121799999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39877,23 +39705,23 @@
       </c>
       <c r="C8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.69811791722499039</v>
+        <v>0.69811782303108516</v>
       </c>
       <c r="D8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.69811791722499039</v>
+        <v>0.69811782303108516</v>
       </c>
       <c r="E8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.64641387777733006</v>
+        <v>0.64641386601512119</v>
       </c>
       <c r="F8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.69113135431235784</v>
+        <v>0.69113126197764607</v>
       </c>
       <c r="G8" s="52">
         <f>IFERROR(1-_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE), "")</f>
-        <v>0.75698345933007127</v>
+        <v>0.75698353047258626</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39902,23 +39730,23 @@
       </c>
       <c r="C9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(C10:C11), 0, 1) + 1, 0, 1, TRUE) - SUM(C10:C11), "")</f>
-        <v>0.2375002167750096</v>
+        <v>0.23750027696891479</v>
       </c>
       <c r="D9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(D10:D11), 0, 1) + 1, 0, 1, TRUE) - SUM(D10:D11), "")</f>
-        <v>0.2375002167750096</v>
+        <v>0.23750027696891479</v>
       </c>
       <c r="E9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(E10:E11), 0, 1) + 1, 0, 1, TRUE) - SUM(E10:E11), "")</f>
-        <v>0.26912212712267003</v>
+        <v>0.26912213398487883</v>
       </c>
       <c r="F9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(F10:F11), 0, 1) + 1, 0, 1, TRUE) - SUM(F10:F11), "")</f>
-        <v>0.24193957968764224</v>
+        <v>0.24193963802235391</v>
       </c>
       <c r="G9" s="52">
         <f>IFERROR(_xlfn.NORM.DIST(_xlfn.NORM.INV(SUM(G10:G11), 0, 1) + 1, 0, 1, TRUE) - SUM(G10:G11), "")</f>
-        <v>0.19813341916992866</v>
+        <v>0.19813336952741373</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39926,19 +39754,19 @@
         <v>119</v>
       </c>
       <c r="C10" s="45">
-        <v>4.1086869000000012E-2</v>
+        <v>4.1086900000000003E-2</v>
       </c>
       <c r="D10" s="53">
-        <v>4.1086869000000012E-2</v>
+        <v>4.1086900000000003E-2</v>
       </c>
       <c r="E10" s="53">
-        <v>7.7459320999999998E-2</v>
+        <v>7.7459300000000009E-2</v>
       </c>
       <c r="F10" s="53">
-        <v>4.8488903E-2</v>
+        <v>4.8488900000000001E-2</v>
       </c>
       <c r="G10" s="53">
-        <v>3.8238834999999999E-2</v>
+        <v>3.8238800000000003E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -39946,19 +39774,19 @@
         <v>120</v>
       </c>
       <c r="C11" s="45">
-        <v>2.3294997000000001E-2</v>
+        <v>2.3295E-2</v>
       </c>
       <c r="D11" s="53">
-        <v>2.3294997000000001E-2</v>
+        <v>2.3295E-2</v>
       </c>
       <c r="E11" s="53">
-        <v>7.0046741000000003E-3</v>
+        <v>7.0047E-3</v>
       </c>
       <c r="F11" s="53">
-        <v>1.8440162999999999E-2</v>
+        <v>1.84402E-2</v>
       </c>
       <c r="G11" s="53">
-        <v>6.6442864999999999E-3</v>
+        <v>6.6442999999999997E-3</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -40135,7 +39963,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vLU7s2lH+dGyWSogBCBHjV5BOgINlXyYdohaaTwAsNrgOgIgnUpv7VGUrl07s3w+SwsCeFFeYHn8Z2zvyhv/9Q==" saltValue="d58si1TRQcTghAeurqjvvw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jImAdMp6XalMcw4f8x60+jkZ4jLSvUAwQ2pEdUIph/a1S5QrVKg+N1iEhRFzx4y2jpe/29TWlf0V4+4tAx9P6g==" saltValue="qROVy/ttmogatkY4MDWYEQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40157,7 +39985,7 @@
     <row r="1" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="str">
         <f>"Pourcentage des enfants dans chaque catégorie pendant l'année de référence ("&amp;start_year&amp;")"</f>
-        <v>Pourcentage des enfants dans chaque catégorie pendant l'année de référence (2021)</v>
+        <v>Pourcentage des enfants dans chaque catégorie pendant l'année de référence (2024)</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>110</v>
@@ -40191,9 +40019,15 @@
       <c r="D2" s="53">
         <v>7.7588900000000002E-2</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
+      <c r="E2" s="53">
+        <v>0</v>
+      </c>
+      <c r="F2" s="53">
+        <v>0</v>
+      </c>
+      <c r="G2" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -40205,9 +40039,15 @@
       <c r="D3" s="53">
         <v>0.15188209999999999</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
+      <c r="E3" s="53">
+        <v>0</v>
+      </c>
+      <c r="F3" s="53">
+        <v>0</v>
+      </c>
+      <c r="G3" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -40217,15 +40057,17 @@
         <v>0.38233679999999998</v>
       </c>
       <c r="D4" s="53">
-        <v>0.4893575</v>
+        <v>0.48935740000000011</v>
       </c>
       <c r="E4" s="53">
-        <v>0.48359873890876798</v>
+        <v>0.47310200000000002</v>
       </c>
       <c r="F4" s="53">
-        <v>0.173986151814461</v>
-      </c>
-      <c r="G4" s="53"/>
+        <v>0.22597100000000001</v>
+      </c>
+      <c r="G4" s="53">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
@@ -40239,11 +40081,11 @@
       </c>
       <c r="E5" s="52">
         <f>1-SUM(E2:E4)</f>
-        <v>0.51640126109123208</v>
+        <v>0.52689799999999998</v>
       </c>
       <c r="F5" s="52">
         <f>1-SUM(F2:F4)</f>
-        <v>0.82601384818553902</v>
+        <v>0.77402899999999997</v>
       </c>
       <c r="G5" s="52">
         <f>1-SUM(G2:G4)</f>
@@ -40251,7 +40093,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FhBSeUaAEaiqKEe2t3RW4lcwbVbrsPBB0z2C5IGJHeEIcCrF71CqReNfElF3fJqVjxzwjkPaa9AIwR6m5QYR2g==" saltValue="XyK/BkI3CyHoWoFqt8HPDg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CHW8l+nqUl/flvhRn502dC+++oGOSzjm4LnDkD5iY+L2rPfdxrjM8rprRIqv+wOk29dq79LOPqJ2DU3uKzgYLg==" saltValue="lUYqmIbRGysJo0R0+jhvAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40304,7 +40146,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>134</v>
       </c>
@@ -40321,10 +40163,10 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -40341,10 +40183,10 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -40361,7 +40203,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
     </row>
-    <row r="7" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>100</v>
       </c>
@@ -40375,7 +40217,7 @@
       <c r="J7" s="23"/>
       <c r="K7" s="23"/>
     </row>
-    <row r="8" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>137</v>
       </c>
@@ -40389,7 +40231,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="10" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -40406,7 +40248,7 @@
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
     </row>
-    <row r="11" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>140</v>
       </c>
@@ -40420,7 +40262,7 @@
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
     </row>
-    <row r="13" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>43</v>
       </c>
@@ -40437,7 +40279,7 @@
       <c r="J13" s="23"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" spans="1:11" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>142</v>
       </c>
@@ -40452,7 +40294,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6z8NWYpaYSEY6CXOY09E0IA2fRVhp9WaO9PBQg7Xz8H7RQ1616t5kPGMYFcHkJdPC6ZxvBnfBZFQFzAxOMp6ig==" saltValue="9Vd7YfTcpMVGYivhSL7O7w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KYiOyqgEuWvnqkR0Y8U3u1sJ7nhMI9KwGWp+ydtHLBqRu2mXqdrfgBAPcJ+IvL7qVSTBkqQymLgE4IFQU+bR0Q==" saltValue="yj7horfZfTwOb78SM80MwA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -40478,7 +40320,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>145</v>
       </c>
@@ -40486,7 +40328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>150</v>
       </c>
@@ -40494,7 +40336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>146</v>
       </c>
@@ -40502,7 +40344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>147</v>
       </c>
@@ -40510,7 +40352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>148</v>
       </c>
@@ -40518,7 +40360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>149</v>
       </c>
@@ -40527,7 +40369,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QlpXeucxO/fFq5V/21j45UArkMpXn4z1XP3nEka/3iYn/TRQBWT23PrYw22STRZwqMXlekzryIDfMHuKK+1Iqg==" saltValue="4BnVHWP5qls28Sh+ctufuQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bsCA1z0nkUn/bWjCBC+2IKH3l2UhfLseLX/iec8CfQ67UYOqpsAav3JyWY14P+i6yQTSJk0obl2/+Siyx+tZ3A==" saltValue="7zgTBClNSKp/iP6i3x63ww==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40579,7 +40421,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>109</v>
       </c>
@@ -40592,7 +40434,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="32" t="s">
         <v>96</v>
       </c>
@@ -40605,29 +40447,33 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
+      <c r="D5" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E5" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
         <v>98</v>
       </c>
       <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="D6" s="47" t="s">
+        <v>5</v>
+      </c>
       <c r="E6" s="38" t="str">
         <f>IF(E$7="","",E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="32" t="s">
         <v>156</v>
       </c>
@@ -40649,7 +40495,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="32" t="s">
         <v>109</v>
       </c>
@@ -40660,7 +40506,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="32" t="s">
         <v>96</v>
       </c>
@@ -40671,7 +40517,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="32" t="s">
         <v>97</v>
       </c>
@@ -40684,7 +40530,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="32" t="s">
         <v>98</v>
       </c>
@@ -40697,7 +40543,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B14" s="32" t="s">
         <v>156</v>
       </c>
@@ -40721,7 +40567,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="32" t="s">
         <v>109</v>
       </c>
@@ -40734,7 +40580,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="32" t="s">
         <v>96</v>
       </c>
@@ -40747,7 +40593,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="32" t="s">
         <v>97</v>
       </c>
@@ -40760,7 +40606,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="32" t="s">
         <v>98</v>
       </c>
@@ -40773,7 +40619,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="32" t="s">
         <v>156</v>
       </c>
@@ -40782,7 +40628,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zy4BCqT7T1G7CScyBM51XTBwOphPmOVv0XjEskasLJhg5j/Vxgbe0YF5iaosjhaT/IIoFvl+aWjt2lw6fnq+FQ==" saltValue="+H2eha6XiMbzC0E5hL5Ajw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="GeJdFUHYuSfe1yInP7CQ6M94NqWNxpFm49LlfL+TnMQmvmbSf/A0qp4IJCsLMcbJqKSbuPtghildR7CgNY3HVA==" saltValue="f2OZCgLn9cpB9Cc/uxtQGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -40841,7 +40687,7 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hDED16vW224q3BWCVwGgORFwOPOaTPV+DfRzCjpmCk0NaDU/pqFCVvNw1U0X5BeYLbu83+AbzNCsg5dokX3VHg==" saltValue="VrRHNb0tK1geyFeR5T3JLw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HXm5rCEWEtCuucSeCWKRWZjhSCnuzBWMNGoGeFahvvWGEzFpBrWs6d6mKQj3900MMQQ0IbH7DBoJmouJqxqsRg==" saltValue="1DD6kmSm2rf5GRr/BjjlFQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/inputs/fr/LiST countries/SYR_databook.xlsx
+++ b/inputs/fr/LiST countries/SYR_databook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tharindu.wickram\Desktop\Modeling\2025 studies\Nutrition\inputs\fr\LiST countries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modelling projects\Nutrition\inputs\fr\LiST countries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2ACA2FB5-E0D0-49A7-AC53-4B39E630A826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92166CE5-FFB8-4155-A00D-64E6486E50D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="961" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Données pop de l'année de ref" sheetId="1" r:id="rId1"/>
@@ -2690,6 +2690,74 @@
         </r>
       </text>
     </comment>
+    <comment ref="L37" authorId="1" shapeId="0" xr:uid="{B53E2CCE-449F-4B13-937B-3F8B887F6752}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="1" shapeId="0" xr:uid="{1148A5A1-251A-4064-B40F-0C8735779040}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="1" shapeId="0" xr:uid="{15C867EE-F338-4C14-9C7D-F0E3CF1EF5FB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O37" authorId="1" shapeId="0" xr:uid="{8E4E4ECE-5F5C-4FD8-8945-6257CBFF139B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Nick Scott:
+Not statistically significantly different to IFAS
+MMS vs I/IFA
+Oh et al 2020, RR 1.02 (0.95-1.10)
+Keats et al 2019, RR 1.04 (0.94-1.15)  </t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000067000000}">
       <text>
         <r>
@@ -3928,7 +3996,7 @@
     <author>Nick Scott</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{6BB5D3EA-EB2C-4557-A77A-BC3B31DE5A74}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{E6EBA730-3C9A-42F5-8372-C12E3D2BCF23}">
       <text>
         <r>
           <rPr>
@@ -3942,7 +4010,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8276B184-5391-46AC-9017-CD45ED68E7E2}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{AF9DB01E-B712-4A66-A517-1C057B372D40}">
       <text>
         <r>
           <rPr>
@@ -3956,7 +4024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{70662288-9B2B-4D49-A059-B389A408D887}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{207C9149-2C56-40E5-890F-83153B938A2F}">
       <text>
         <r>
           <rPr>
@@ -3970,7 +4038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{5F99FF59-4E44-4847-82EE-D42B7418AA00}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{39C4CB92-7EE0-4046-B67E-41191387FFA0}">
       <text>
         <r>
           <rPr>
@@ -3984,7 +4052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{F6C9465E-FBDE-45D1-8394-CD6F9C9C2529}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{E377B1E7-A333-4A74-97C3-029328512C07}">
       <text>
         <r>
           <rPr>
@@ -3998,7 +4066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{8724D448-9507-4D14-BCA7-F21B3CAF1BD6}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{200C4BAB-9EE2-447E-A6DD-80717CFE4AC8}">
       <text>
         <r>
           <rPr>
@@ -4012,7 +4080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{1D086CE7-3639-4C5A-8FD3-DB935503731C}">
+    <comment ref="F6" authorId="1" shapeId="0" xr:uid="{9FC7E5D2-2D8B-4961-9B75-5691D4A68B0C}">
       <text>
         <r>
           <rPr>
@@ -4026,7 +4094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{1EDBAC82-3035-4B47-8DB4-6C9605D373FF}">
+    <comment ref="G6" authorId="1" shapeId="0" xr:uid="{D951D76C-28E5-48CE-899C-D128152950FC}">
       <text>
         <r>
           <rPr>
@@ -4040,7 +4108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{F889FFDD-F5D3-428F-97C9-3FA317F4DEEC}">
+    <comment ref="F8" authorId="1" shapeId="0" xr:uid="{E9DCEC9B-12F6-42CF-8CD9-B1C5DD42DE71}">
       <text>
         <r>
           <rPr>
@@ -4054,7 +4122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{178C61B9-10CF-475E-AE2A-1148BD159501}">
+    <comment ref="G8" authorId="1" shapeId="0" xr:uid="{9FD33C3F-D78F-4E9D-A67C-9D39AC73491A}">
       <text>
         <r>
           <rPr>
@@ -4068,7 +4136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{D1ADD6AA-00B3-496F-889D-6AD9E8EC7261}">
+    <comment ref="F10" authorId="1" shapeId="0" xr:uid="{3400288E-DF03-41FF-B1F2-3EB20AA1B927}">
       <text>
         <r>
           <rPr>
@@ -4082,7 +4150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{D8A7821F-2C8B-4B9F-B2CF-783B6F1D6ACB}">
+    <comment ref="G10" authorId="1" shapeId="0" xr:uid="{9C325214-076C-49F4-9A1C-FDD39C7EF1F6}">
       <text>
         <r>
           <rPr>
@@ -4096,7 +4164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{30A88894-D578-48EA-8642-A1FBFF69A3C1}">
+    <comment ref="F12" authorId="1" shapeId="0" xr:uid="{9B6733C4-FA93-4154-8674-5B85D19B6115}">
       <text>
         <r>
           <rPr>
@@ -4110,7 +4178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{1FC0B5F8-9FC2-4095-AEC3-321F62EB13E4}">
+    <comment ref="G12" authorId="1" shapeId="0" xr:uid="{0607EB3C-B9C7-4D01-AE82-3B20B34591B6}">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{037243D6-BCDE-4F6B-AFCC-3F94A0DD5E02}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{26DD0551-BD1F-450A-8953-951E786BA725}">
       <text>
         <r>
           <rPr>
@@ -4138,7 +4206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{DE335ADC-5DD3-496C-A5AC-AAE47036457E}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{07B0F43C-E3A4-41A5-9220-14111D4DE5D5}">
       <text>
         <r>
           <rPr>
@@ -4152,7 +4220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{2912EBE3-D556-42B6-96D5-24EC21E6156C}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{BF774CA2-E4B3-46E6-A04D-901C8156EE77}">
       <text>
         <r>
           <rPr>
@@ -4166,7 +4234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{4CB9182B-79CD-4596-8295-56AF4E3846AB}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{DDFF231A-B050-4E30-B877-4FB8473D71B0}">
       <text>
         <r>
           <rPr>
@@ -4180,7 +4248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{80F6289A-949B-4FAE-AC85-22980BCEA4F4}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{0214BC76-CC8A-414C-8D7A-C51B3E742D6B}">
       <text>
         <r>
           <rPr>
@@ -4204,7 +4272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{96FCBC9B-E5EC-46B8-8DF3-3E8D35EE350D}">
+    <comment ref="F20" authorId="1" shapeId="0" xr:uid="{408E5496-8B3D-4F1E-BD84-9A9255C25832}">
       <text>
         <r>
           <rPr>
@@ -4218,7 +4286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{93171B53-CE10-41E2-9E96-E27147D4D778}">
+    <comment ref="F22" authorId="1" shapeId="0" xr:uid="{DF0EEE5A-AAEC-4832-9B3D-B069B0FD3D24}">
       <text>
         <r>
           <rPr>
@@ -4232,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{5FE03E37-E69F-43F4-B94E-7BBC3063A87D}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{2A9C86D6-9952-4010-8EF5-ED482E1554FE}">
       <text>
         <r>
           <rPr>
@@ -4247,7 +4315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{626B60BA-B78A-4BE5-ACC0-D15C014DDDE7}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{5A70274A-2FB2-4238-A065-120459AD1B15}">
       <text>
         <r>
           <rPr>
@@ -4262,7 +4330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{A6D7FDB2-70C1-4A3F-AE05-E1F583DAC911}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{385F9BE4-A3AC-4198-BAC3-722E7A520402}">
       <text>
         <r>
           <rPr>
@@ -4277,7 +4345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{73FE6ADA-DBBD-4E18-9E0A-7E9F1B65F4FF}">
+    <comment ref="D30" authorId="1" shapeId="0" xr:uid="{1E0B57C8-7A0A-48E3-A3E8-1E19A7175498}">
       <text>
         <r>
           <rPr>
@@ -4292,7 +4360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{36DC02C6-7D52-483D-9E4D-A62E1832D1E9}">
+    <comment ref="E30" authorId="1" shapeId="0" xr:uid="{2AC9637A-4534-4154-9BD7-3AE7DD8CD9DD}">
       <text>
         <r>
           <rPr>
@@ -4307,7 +4375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{3A418ECB-CB98-4DAE-914F-181BDF7ED565}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{01A3CEF9-0D30-4FDB-AF26-2DC31C7D29F6}">
       <text>
         <r>
           <rPr>
@@ -4322,7 +4390,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{F54E6507-D7CB-4F8D-8BA0-8C678AC88484}">
+    <comment ref="G30" authorId="1" shapeId="0" xr:uid="{E3448607-813B-4893-BFAF-1777B6724FBF}">
       <text>
         <r>
           <rPr>
@@ -4337,7 +4405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{51D136EC-624C-44D3-B5B3-53EE7A4C79F4}">
+    <comment ref="H30" authorId="1" shapeId="0" xr:uid="{CB33591A-EF28-41CE-A9F1-ECF332B1A04F}">
       <text>
         <r>
           <rPr>
@@ -4352,7 +4420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{0358037B-23C7-469B-B136-BD3C312D371A}">
+    <comment ref="D45" authorId="0" shapeId="0" xr:uid="{652EDCEE-9F4F-4011-BE3F-87A81AEAB68F}">
       <text>
         <r>
           <rPr>
@@ -4366,7 +4434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{83DD7CE2-EBA6-4C72-A5A2-1E7961104F35}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{F2E7DF39-BD3C-4774-9BD5-66837E9E22BF}">
       <text>
         <r>
           <rPr>
@@ -4380,7 +4448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{D00C0728-6CE5-4232-9E9D-03298AA7E83F}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{84346A43-22E1-4209-86B7-5484553C9A3C}">
       <text>
         <r>
           <rPr>
@@ -4394,7 +4462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{DE005C0A-2F8A-418C-851E-64B2B8CFE1FA}">
+    <comment ref="G45" authorId="0" shapeId="0" xr:uid="{6AA73D8B-E906-4C63-9A89-433F265EDADB}">
       <text>
         <r>
           <rPr>
@@ -4408,7 +4476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{E55324F7-370C-4385-ADBA-E8B0EBEB4BEC}">
+    <comment ref="H45" authorId="0" shapeId="0" xr:uid="{D0DB495D-46B4-4957-B9C2-D1B5214046C5}">
       <text>
         <r>
           <rPr>
@@ -4422,7 +4490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{F53439F8-F18B-45A1-B265-14A4B9BFCA4E}">
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{E8F934AE-F36A-4978-A2B4-5231B12CD33F}">
       <text>
         <r>
           <rPr>
@@ -4436,7 +4504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{D3552897-BBD5-4175-B68A-A3F1E4A6E75C}">
+    <comment ref="E46" authorId="0" shapeId="0" xr:uid="{53D9CECE-9FA0-4330-B76A-C6EEC6C1D659}">
       <text>
         <r>
           <rPr>
@@ -4450,7 +4518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{CC47941B-D047-44AD-8609-225A3A1207CF}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{9DC905D6-8DE5-4FE7-BE6F-D3E934A75201}">
       <text>
         <r>
           <rPr>
@@ -4464,7 +4532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{0CBE3706-3924-4509-A583-88069D4C218C}">
+    <comment ref="G46" authorId="0" shapeId="0" xr:uid="{ACC4B3F7-E558-402F-BE57-0C3DDC8060F5}">
       <text>
         <r>
           <rPr>
@@ -4478,7 +4546,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{A5F6F3D3-D70F-4D04-A795-6D6BF5E34983}">
+    <comment ref="H46" authorId="0" shapeId="0" xr:uid="{955FA18E-86F7-422C-8CA5-A38FE4881347}">
       <text>
         <r>
           <rPr>
@@ -4492,7 +4560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{DD598447-A738-4E83-BE84-12132D14A7E3}">
+    <comment ref="D49" authorId="0" shapeId="0" xr:uid="{33441C3A-E101-49E5-A4DB-504F222DBABB}">
       <text>
         <r>
           <rPr>
@@ -4507,7 +4575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{AAC1265A-FBA5-4B61-B6FD-C1ADAB02C015}">
+    <comment ref="E49" authorId="0" shapeId="0" xr:uid="{9A6BDF27-568B-45B9-BE8D-362C80D286A5}">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{CB5BEA38-52BE-4279-8999-876D134092DA}">
+    <comment ref="F49" authorId="0" shapeId="0" xr:uid="{08FA6FC1-5E34-45F1-9F8B-4E7BAEF15D4E}">
       <text>
         <r>
           <rPr>
@@ -4537,7 +4605,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{EEC82E46-7238-472F-8156-89C286EC0CC5}">
+    <comment ref="G49" authorId="0" shapeId="0" xr:uid="{E9730E75-4547-4DE1-A9F2-FCA6D5B09778}">
       <text>
         <r>
           <rPr>
@@ -4552,7 +4620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{9AD99541-38BF-452C-BBDF-30A63672B134}">
+    <comment ref="H49" authorId="0" shapeId="0" xr:uid="{38945CFE-2923-4A7C-9E0E-820E103F12F0}">
       <text>
         <r>
           <rPr>
@@ -4567,7 +4635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{9F2485E2-4FB1-40DF-95BC-EF307614F383}">
+    <comment ref="D51" authorId="0" shapeId="0" xr:uid="{F76610CF-AE5A-4A2B-BD5A-C60057991BBE}">
       <text>
         <r>
           <rPr>
@@ -4583,7 +4651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{5A344499-6486-4E45-BC00-E472735A7CB2}">
+    <comment ref="E51" authorId="0" shapeId="0" xr:uid="{8EC67AD9-5004-458A-B78A-27343190877D}">
       <text>
         <r>
           <rPr>
@@ -4599,7 +4667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{031BB5AD-8138-4687-BD78-7EBC20A98663}">
+    <comment ref="F51" authorId="0" shapeId="0" xr:uid="{8D6C5816-8BDB-4D07-A205-24F2394A4590}">
       <text>
         <r>
           <rPr>
@@ -4615,7 +4683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{184A5B5A-1F15-44FE-898C-B90309E01D89}">
+    <comment ref="G51" authorId="0" shapeId="0" xr:uid="{B76A1BFB-64B6-4C17-9732-138D8EB49340}">
       <text>
         <r>
           <rPr>
@@ -4631,7 +4699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{8ED585B4-389F-460E-8916-C9CBE4D87E3D}">
+    <comment ref="H51" authorId="0" shapeId="0" xr:uid="{962C7931-87AA-452E-BF56-06BF5EBED30C}">
       <text>
         <r>
           <rPr>
@@ -4647,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{AD24A257-1231-432A-9AC2-49A1BBCFE8E5}">
+    <comment ref="D53" authorId="0" shapeId="0" xr:uid="{25F108DC-6C32-4B96-9492-1B12A3709CE9}">
       <text>
         <r>
           <rPr>
@@ -4662,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{A07ED250-D084-453F-8461-66EC0C10E110}">
+    <comment ref="E53" authorId="0" shapeId="0" xr:uid="{8B1376CD-B39F-49F6-BC5B-7A2858E0592C}">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{9059BCA8-1FD3-4E64-86A7-3061E1F307E3}">
+    <comment ref="F53" authorId="0" shapeId="0" xr:uid="{048CF327-553B-4B14-8A84-22CC73D47D4A}">
       <text>
         <r>
           <rPr>
@@ -4692,7 +4760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{7052734F-4036-424E-8991-EAD18C6FC7CF}">
+    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{1FFD936D-DA45-475C-9F30-391304B2787A}">
       <text>
         <r>
           <rPr>
@@ -4707,7 +4775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{9211745A-0C8C-4E89-B62F-2D6F1D5B7D01}">
+    <comment ref="H53" authorId="0" shapeId="0" xr:uid="{3CED59C7-FFD8-4D8E-9210-1FB3B9F57245}">
       <text>
         <r>
           <rPr>
@@ -4722,7 +4790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{5423B35A-FBAB-43E1-A574-44F7790EAEA1}">
+    <comment ref="D55" authorId="1" shapeId="0" xr:uid="{BFC97A30-BB96-4307-90EA-5BE03611C63A}">
       <text>
         <r>
           <rPr>
@@ -4736,7 +4804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{9923839E-0345-401E-8DBE-0D84F514E4A9}">
+    <comment ref="F60" authorId="0" shapeId="0" xr:uid="{51ED88B2-1E5E-47FC-9698-0E5AB645D504}">
       <text>
         <r>
           <rPr>
@@ -4750,7 +4818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{BA7FE3E3-08B4-4F16-B01F-05A523005C56}">
+    <comment ref="G60" authorId="0" shapeId="0" xr:uid="{561CB528-6BAE-4817-8CC0-243735B76FA1}">
       <text>
         <r>
           <rPr>
@@ -4764,7 +4832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{6D26BBC2-8403-47E0-89A8-CCA5B5E2A63F}">
+    <comment ref="H60" authorId="0" shapeId="0" xr:uid="{E496632C-74C0-41C8-9AB4-0B4C87893674}">
       <text>
         <r>
           <rPr>
@@ -4778,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{4063B8B9-975B-4060-938A-48F03FAEF419}">
+    <comment ref="F61" authorId="0" shapeId="0" xr:uid="{FBF69FC4-CD17-4513-AF48-E695A29BF824}">
       <text>
         <r>
           <rPr>
@@ -4792,7 +4860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{50660BAB-9FCC-42B5-9F93-0DBB8CA89897}">
+    <comment ref="G61" authorId="0" shapeId="0" xr:uid="{900E651E-9020-4856-BB60-BF507FACE1CC}">
       <text>
         <r>
           <rPr>
@@ -4806,7 +4874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{C6A07F78-8D75-479F-926E-474BA841B234}">
+    <comment ref="H61" authorId="0" shapeId="0" xr:uid="{49F9B2F7-6FD6-4FDF-921C-425B5CDD5155}">
       <text>
         <r>
           <rPr>
@@ -4820,7 +4888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{FA86AF70-4991-447A-BCAA-1000A44BF256}">
+    <comment ref="F63" authorId="1" shapeId="0" xr:uid="{4AC52846-7242-459E-9C8D-BF78F201C110}">
       <text>
         <r>
           <rPr>
@@ -4834,7 +4902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{FD47D524-CA3E-4654-B95C-882313C71EE4}">
+    <comment ref="G63" authorId="1" shapeId="0" xr:uid="{B7E52F08-0E63-474C-A17D-FB71B12C1A4F}">
       <text>
         <r>
           <rPr>
@@ -4848,7 +4916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{350D10EC-94B3-4790-8891-B0A27313C3E5}">
+    <comment ref="F65" authorId="1" shapeId="0" xr:uid="{329CDC5B-FBD8-45AA-9D30-2F9915F0B0DB}">
       <text>
         <r>
           <rPr>
@@ -4862,7 +4930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{E54F70F0-DBA3-4F25-90EB-D1DFD3641E6A}">
+    <comment ref="G65" authorId="1" shapeId="0" xr:uid="{74D24310-E8B6-4724-B08F-C246A0B86F17}">
       <text>
         <r>
           <rPr>
@@ -4876,7 +4944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{77363AFB-2A43-477F-8EB8-CC2F7E3ECEA0}">
+    <comment ref="F67" authorId="1" shapeId="0" xr:uid="{7026E01B-E53C-4032-904B-4C8C6143328A}">
       <text>
         <r>
           <rPr>
@@ -4890,7 +4958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{01109C22-04ED-4FDB-949C-C34810AB2E95}">
+    <comment ref="G67" authorId="1" shapeId="0" xr:uid="{56E6B52D-1C74-48A6-AB95-D033A5B5881A}">
       <text>
         <r>
           <rPr>
@@ -4904,7 +4972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{72F3E256-254B-4FFC-9E01-1752BCF475A6}">
+    <comment ref="F69" authorId="1" shapeId="0" xr:uid="{A2996F6D-43C2-499B-8B4D-F7E668692366}">
       <text>
         <r>
           <rPr>
@@ -4918,7 +4986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{E057EF81-59F3-42CB-9D3F-907D93019067}">
+    <comment ref="G69" authorId="1" shapeId="0" xr:uid="{1BA30CAA-FFAB-42ED-B857-7C2DBF6DD53A}">
       <text>
         <r>
           <rPr>
@@ -4932,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{DF457454-4973-4207-9E3D-7D50D7830FDE}">
+    <comment ref="F71" authorId="0" shapeId="0" xr:uid="{234E5DD0-50F5-435F-A2AD-FDCE2659B300}">
       <text>
         <r>
           <rPr>
@@ -4946,7 +5014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{0A31E4B1-743B-4208-AE2B-4146BBD81A93}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{81B268C8-266C-41E0-8968-7FD59EF44415}">
       <text>
         <r>
           <rPr>
@@ -4960,7 +5028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{BA5122FC-4C8D-49F0-9902-8C88B2457CA4}">
+    <comment ref="F73" authorId="0" shapeId="0" xr:uid="{D68CDFE1-6866-4AC0-B4D7-B34E1A995637}">
       <text>
         <r>
           <rPr>
@@ -4974,7 +5042,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{EB775666-1A82-4D30-A432-4C033A1A7AED}">
+    <comment ref="G73" authorId="0" shapeId="0" xr:uid="{6447B983-C337-44DD-BE06-3BF10916980C}">
       <text>
         <r>
           <rPr>
@@ -4988,7 +5056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{98BB8C6D-B30B-4DB6-8B35-7D8DCE93E79C}">
+    <comment ref="F77" authorId="1" shapeId="0" xr:uid="{42AC3582-1D7E-471B-A6C7-CD7E77F8588B}">
       <text>
         <r>
           <rPr>
@@ -5003,7 +5071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{75544419-0995-4A7F-98E3-CBE19D6471D0}">
+    <comment ref="F79" authorId="1" shapeId="0" xr:uid="{C499C901-0DF0-4641-8493-EE778DE73B96}">
       <text>
         <r>
           <rPr>
@@ -5018,7 +5086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{866B3636-D1B7-40EE-A9B3-22FD1891C340}">
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{080FF01F-34D3-44B7-835E-C7CC7A5B457C}">
       <text>
         <r>
           <rPr>
@@ -5033,7 +5101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{3C5743BD-EFCC-4AF2-B330-6FDF8775A9D5}">
+    <comment ref="D83" authorId="0" shapeId="0" xr:uid="{B263C3DB-9806-4F53-B7FE-F5AB30086A04}">
       <text>
         <r>
           <rPr>
@@ -5048,7 +5116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{07C4191C-0E34-4B64-AAF8-A7F551741AB2}">
+    <comment ref="D85" authorId="0" shapeId="0" xr:uid="{FF88E7CE-1D54-4693-9AC1-0680C2879226}">
       <text>
         <r>
           <rPr>
@@ -5063,7 +5131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{419B2D75-98C1-46B5-842D-118FC911FF04}">
+    <comment ref="D87" authorId="1" shapeId="0" xr:uid="{F32BE7CD-2AAA-47AD-914F-4CAAC1FEDD3B}">
       <text>
         <r>
           <rPr>
@@ -5078,7 +5146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{A1CD6A7F-EF69-49BD-84EA-F060EB24114F}">
+    <comment ref="E87" authorId="1" shapeId="0" xr:uid="{BCFCAE2C-B071-4EBD-916E-9CB34A3AE95A}">
       <text>
         <r>
           <rPr>
@@ -5093,7 +5161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{D5825461-688C-438C-8542-BD85D579FDC7}">
+    <comment ref="F87" authorId="1" shapeId="0" xr:uid="{E2890E16-5EE9-49DE-B974-B3ADDC0025FE}">
       <text>
         <r>
           <rPr>
@@ -5108,7 +5176,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{AF7C92B2-AC28-43C3-9C19-D68E37FF28FD}">
+    <comment ref="G87" authorId="1" shapeId="0" xr:uid="{FFC68E24-6D1B-4208-B66E-D8A12166F7EF}">
       <text>
         <r>
           <rPr>
@@ -5123,7 +5191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{700142E9-6A7D-415A-8AA2-F2A8B6A75555}">
+    <comment ref="H87" authorId="1" shapeId="0" xr:uid="{AE98D75E-0886-4415-A5FC-355EDA6C4FF5}">
       <text>
         <r>
           <rPr>
@@ -5138,7 +5206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{7D67AB3C-983B-47D0-9AFF-DA097636CBA4}">
+    <comment ref="D103" authorId="0" shapeId="0" xr:uid="{F3FF4EFF-507E-406A-9019-C50AD187D27F}">
       <text>
         <r>
           <rPr>
@@ -5152,7 +5220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{38FC6B21-5384-4027-AE29-F2FF12011A26}">
+    <comment ref="E103" authorId="0" shapeId="0" xr:uid="{DE5B9A2C-A2CF-41B4-A227-60CE716BCCA3}">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{EB3D123B-E86C-4173-B872-21E041277078}">
+    <comment ref="F103" authorId="0" shapeId="0" xr:uid="{34EEDC69-740F-43FD-A983-6FB9711FB123}">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C5BAFDF7-3C0B-454A-B8DD-17A5272728F7}">
+    <comment ref="G103" authorId="0" shapeId="0" xr:uid="{C1C7CF2A-6820-4496-B5B3-46A027800BF9}">
       <text>
         <r>
           <rPr>
@@ -5194,7 +5262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{BB84B4E6-6EBF-43F8-A27F-ABACD68A728A}">
+    <comment ref="H103" authorId="0" shapeId="0" xr:uid="{EBC10A23-30BF-4E42-8CA2-8EE10D6CA31A}">
       <text>
         <r>
           <rPr>
@@ -5208,7 +5276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{BFD18A89-7D4A-4FA5-8D9C-46BDFC49F7B4}">
+    <comment ref="D106" authorId="0" shapeId="0" xr:uid="{C4570B06-D8B9-4BF0-8899-481D28F107D4}">
       <text>
         <r>
           <rPr>
@@ -5223,7 +5291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{1ABF9016-F3C2-48B1-BD46-AD89F4003AC8}">
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{E10AAA50-CCAF-4DFB-8CEA-438EA6695142}">
       <text>
         <r>
           <rPr>
@@ -5238,7 +5306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{6A6E8E29-2989-40FF-B168-55803883F0D8}">
+    <comment ref="F106" authorId="0" shapeId="0" xr:uid="{0D2DBAA3-0B85-4069-9696-DDECC83557DF}">
       <text>
         <r>
           <rPr>
@@ -5253,7 +5321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{48DA76B4-3665-4A45-819A-BFEEFF70E5D8}">
+    <comment ref="G106" authorId="0" shapeId="0" xr:uid="{E6F4F3F2-6816-43AD-9558-8D77B03CE641}">
       <text>
         <r>
           <rPr>
@@ -5268,7 +5336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{B80ED8C6-87BC-498B-8629-005BCCE79F4B}">
+    <comment ref="H106" authorId="0" shapeId="0" xr:uid="{994813E0-DC6E-4867-8FA2-13765D152F5E}">
       <text>
         <r>
           <rPr>
@@ -5283,7 +5351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{B5F2ED77-4534-4005-9653-3943813A8B21}">
+    <comment ref="D108" authorId="0" shapeId="0" xr:uid="{6D709644-E2DA-4998-B8D6-CCE8241FA062}">
       <text>
         <r>
           <rPr>
@@ -5299,7 +5367,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{76285A74-606B-4904-9089-8C072E19A125}">
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{E0BF8484-6C50-4B90-B5C7-81D81EF18053}">
       <text>
         <r>
           <rPr>
@@ -5315,7 +5383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{63134AD8-900C-4178-BB9D-773F5A2AEB3B}">
+    <comment ref="F108" authorId="0" shapeId="0" xr:uid="{98B23DB2-DC71-4976-B9E0-A2E971751C45}">
       <text>
         <r>
           <rPr>
@@ -5331,7 +5399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{E4550204-DAD5-4F24-9613-4B653BB1BEF9}">
+    <comment ref="G108" authorId="0" shapeId="0" xr:uid="{EED7AE56-914C-4919-99D9-9B4DD94D01A5}">
       <text>
         <r>
           <rPr>
@@ -5347,7 +5415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{8EB04C99-52A7-4C56-9738-8833ED4CF79E}">
+    <comment ref="H108" authorId="0" shapeId="0" xr:uid="{C946989D-0B8C-452F-9FD8-02724BD02182}">
       <text>
         <r>
           <rPr>
@@ -5363,7 +5431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{1E087D6A-9C87-4366-B106-9662D0E9F522}">
+    <comment ref="D110" authorId="0" shapeId="0" xr:uid="{E509D43A-5096-49C2-BA18-0C199C6BF4A8}">
       <text>
         <r>
           <rPr>
@@ -5378,7 +5446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{9524A10F-3B35-4B50-9361-07DEAF9EC66F}">
+    <comment ref="E110" authorId="0" shapeId="0" xr:uid="{7D8578B9-425B-43DC-B215-7EF10F08E80C}">
       <text>
         <r>
           <rPr>
@@ -5393,7 +5461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{00995C78-B5BF-45A5-8F02-B4D6CB8053C5}">
+    <comment ref="F110" authorId="0" shapeId="0" xr:uid="{309E82E0-67AD-454E-9A05-4D9313B66A93}">
       <text>
         <r>
           <rPr>
@@ -5408,7 +5476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B614B807-4445-457C-8B76-0D078F087764}">
+    <comment ref="G110" authorId="0" shapeId="0" xr:uid="{B9EF8017-E5A0-4B1E-9AF7-1E695ECA49AB}">
       <text>
         <r>
           <rPr>
@@ -5423,7 +5491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{4A9ECB14-4CB2-41BF-A402-F7A28029EC10}">
+    <comment ref="H110" authorId="0" shapeId="0" xr:uid="{26E77479-1563-4266-B2C1-17AF174C9575}">
       <text>
         <r>
           <rPr>
@@ -5438,7 +5506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{B642BE55-802D-4C94-B750-1AEA253BACA7}">
+    <comment ref="D112" authorId="1" shapeId="0" xr:uid="{09D666FE-E28F-48AE-ADF8-2D96C595DB94}">
       <text>
         <r>
           <rPr>
@@ -5452,7 +5520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{CE9B9D72-3B1C-4412-9D79-6D0874D60CEE}">
+    <comment ref="F117" authorId="0" shapeId="0" xr:uid="{B9267817-21CE-42E6-A675-E3EF4A926E99}">
       <text>
         <r>
           <rPr>
@@ -5466,7 +5534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{AB5427B8-7880-46F7-8737-0E11C545B3E1}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{D5F41D35-9589-4734-9273-1246C82D90D3}">
       <text>
         <r>
           <rPr>
@@ -5480,7 +5548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{7DADC3D7-B312-4F80-917D-FD030194B70F}">
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{68C36586-6425-44D5-AE71-7B83AC0B0D80}">
       <text>
         <r>
           <rPr>
@@ -5494,7 +5562,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{E932DAA3-B84B-48A0-A350-BB68775D7800}">
+    <comment ref="F118" authorId="0" shapeId="0" xr:uid="{EAF8C373-AE13-4606-898A-ED625C16452F}">
       <text>
         <r>
           <rPr>
@@ -5508,7 +5576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{75AFBBA3-C0BF-47C9-96C1-E2BCE0A5518C}">
+    <comment ref="G118" authorId="0" shapeId="0" xr:uid="{A99AB4B1-F894-4133-B7CD-69537AC87FC8}">
       <text>
         <r>
           <rPr>
@@ -5522,7 +5590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{44B4DAC8-1128-45E5-B99C-C84974BBEE0A}">
+    <comment ref="H118" authorId="0" shapeId="0" xr:uid="{66812343-2E7C-44E8-B27C-8CF88CE05138}">
       <text>
         <r>
           <rPr>
@@ -5536,7 +5604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{BFC250B8-BAEB-445C-954D-7BE97AABDFDB}">
+    <comment ref="F120" authorId="1" shapeId="0" xr:uid="{384DF3D1-4AA8-4943-A530-5AAE715E42E7}">
       <text>
         <r>
           <rPr>
@@ -5550,7 +5618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{AEC7DAF2-9B1C-4CBB-B735-E9AB7A0CFD03}">
+    <comment ref="G120" authorId="1" shapeId="0" xr:uid="{1DE26347-7149-43FD-858E-465A040CC0F3}">
       <text>
         <r>
           <rPr>
@@ -5564,7 +5632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{5757C298-3224-4FCB-AE44-57AE2804657A}">
+    <comment ref="F122" authorId="1" shapeId="0" xr:uid="{B687D13E-D130-42E7-9D6A-3F80F0C7EF5D}">
       <text>
         <r>
           <rPr>
@@ -5578,7 +5646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{32018E11-B6CC-4CB9-AD83-CDEAB15CB02F}">
+    <comment ref="G122" authorId="1" shapeId="0" xr:uid="{9BC31D67-F810-46D7-B5A1-4288AAC1F5B6}">
       <text>
         <r>
           <rPr>
@@ -5592,7 +5660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{548CA939-8049-4A22-8DCF-97B43275D455}">
+    <comment ref="F124" authorId="1" shapeId="0" xr:uid="{64D245B3-8DA5-40BE-BC14-2456737D9F8E}">
       <text>
         <r>
           <rPr>
@@ -5606,7 +5674,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{B79D2BBE-1689-4CA2-9F3C-27F21A096995}">
+    <comment ref="G124" authorId="1" shapeId="0" xr:uid="{5798986F-DE4D-469D-8D38-C4A254954155}">
       <text>
         <r>
           <rPr>
@@ -5620,7 +5688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{521B8842-9FA3-4AE6-9999-7E38BD5734E2}">
+    <comment ref="F126" authorId="1" shapeId="0" xr:uid="{1683DE01-9F25-40E0-AE29-344104540630}">
       <text>
         <r>
           <rPr>
@@ -5634,7 +5702,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{745C521C-CEC3-4590-B658-F244E03502B3}">
+    <comment ref="G126" authorId="1" shapeId="0" xr:uid="{6E399964-9FF6-4F4D-B47E-AC805C54B9BA}">
       <text>
         <r>
           <rPr>
@@ -5648,7 +5716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{48501DF5-33AD-4137-BF61-A1ACEF3712BB}">
+    <comment ref="F128" authorId="0" shapeId="0" xr:uid="{EFF89D0F-5E10-4447-B0BA-64F660AD6D14}">
       <text>
         <r>
           <rPr>
@@ -5662,7 +5730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{52DA180B-0E50-41F0-B433-76D057FD32AA}">
+    <comment ref="G128" authorId="0" shapeId="0" xr:uid="{E024415B-2F81-4A00-9886-75203AC76837}">
       <text>
         <r>
           <rPr>
@@ -5676,7 +5744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{1827DF80-3E7F-4FAE-B545-321A48A20B7F}">
+    <comment ref="F130" authorId="0" shapeId="0" xr:uid="{773BC8B9-C7FD-4E1D-BFAD-28167A2B0241}">
       <text>
         <r>
           <rPr>
@@ -5690,7 +5758,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{428ADF28-94CB-45A6-B512-653753D79D4A}">
+    <comment ref="G130" authorId="0" shapeId="0" xr:uid="{E0893EE6-8215-43BF-B8DC-C2BA125EF501}">
       <text>
         <r>
           <rPr>
@@ -5704,7 +5772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{E327363C-87BF-426D-8031-8E5B15B868F6}">
+    <comment ref="F134" authorId="1" shapeId="0" xr:uid="{B0106407-B25E-404E-AE98-C6E846DE7439}">
       <text>
         <r>
           <rPr>
@@ -5719,7 +5787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{0FC0F10D-E16C-4929-8C9C-BBCE7D585B2C}">
+    <comment ref="F136" authorId="1" shapeId="0" xr:uid="{B3781CC1-6735-4678-95E3-B6650A0CF979}">
       <text>
         <r>
           <rPr>
@@ -5734,7 +5802,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{83AA2241-D1A0-473B-BB01-4502DE008F6C}">
+    <comment ref="D138" authorId="0" shapeId="0" xr:uid="{550CF970-1632-472E-99A6-5157A6C70FB5}">
       <text>
         <r>
           <rPr>
@@ -5749,7 +5817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{AB840D19-E9DC-41E5-8B1A-28772D27BB6F}">
+    <comment ref="D140" authorId="0" shapeId="0" xr:uid="{0F529DF4-B0D9-4A77-880D-52378457049B}">
       <text>
         <r>
           <rPr>
@@ -5764,7 +5832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{28DA7237-5B4A-4888-B612-1517D8E4181A}">
+    <comment ref="D142" authorId="0" shapeId="0" xr:uid="{0A749486-D0DA-44DD-A158-4937B013D9E1}">
       <text>
         <r>
           <rPr>
@@ -5779,7 +5847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{24B15358-0318-4650-A1D9-ACBF45D6BD86}">
+    <comment ref="D144" authorId="1" shapeId="0" xr:uid="{65A87F96-9920-4AFF-9D42-432A9BC46A37}">
       <text>
         <r>
           <rPr>
@@ -5794,7 +5862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{3CCBD856-2028-4562-873C-EF798B7CEB0E}">
+    <comment ref="E144" authorId="1" shapeId="0" xr:uid="{14AFEBEB-6E6D-485B-AD84-D77832449F6B}">
       <text>
         <r>
           <rPr>
@@ -5809,7 +5877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{515C103F-DDC3-40D5-AA24-3704C957FBDF}">
+    <comment ref="F144" authorId="1" shapeId="0" xr:uid="{C956521D-520C-46E0-BBF9-22BA4AB5823B}">
       <text>
         <r>
           <rPr>
@@ -5824,7 +5892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{2B07245A-D9DE-402F-8C94-59F9204780AD}">
+    <comment ref="G144" authorId="1" shapeId="0" xr:uid="{889435D0-F1CE-49D5-B3FA-2C346C3DD8BB}">
       <text>
         <r>
           <rPr>
@@ -5839,7 +5907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{B09F6ACE-9930-4B23-AC49-D976E3AF6D20}">
+    <comment ref="H144" authorId="1" shapeId="0" xr:uid="{21DCB560-D7D0-454D-9256-2EB6BA5D9FAF}">
       <text>
         <r>
           <rPr>
@@ -5854,7 +5922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{08D07A70-B0BF-4318-BF4F-F0DBC6170F84}">
+    <comment ref="D160" authorId="0" shapeId="0" xr:uid="{2CA48B3A-F458-496E-A12E-9EDFF9710F14}">
       <text>
         <r>
           <rPr>
@@ -5868,7 +5936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{76EC0005-9898-4CC7-A802-EC15F25448F0}">
+    <comment ref="E160" authorId="0" shapeId="0" xr:uid="{D5130B5B-6564-4541-AFF7-B31DC2A99F0C}">
       <text>
         <r>
           <rPr>
@@ -5882,7 +5950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{E5FFA232-5153-4095-946B-DFA45A9FBF8C}">
+    <comment ref="F160" authorId="0" shapeId="0" xr:uid="{A87CEC0D-D5EC-411A-9E0A-45792CF26B1E}">
       <text>
         <r>
           <rPr>
@@ -5896,7 +5964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{AFCCFA07-E0EB-45D3-B7C0-514815792647}">
+    <comment ref="G160" authorId="0" shapeId="0" xr:uid="{F07A7990-2D7C-41E0-8069-25EED27A8B7D}">
       <text>
         <r>
           <rPr>
@@ -5910,7 +5978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{C392BCAD-8C69-4A4C-87EF-377772EECC28}">
+    <comment ref="H160" authorId="0" shapeId="0" xr:uid="{B9A5DC53-F533-4CB3-94F1-5C0DF398AC61}">
       <text>
         <r>
           <rPr>
@@ -5924,7 +5992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{E3317A10-0BE4-48FF-9352-A01B5BA3FEE5}">
+    <comment ref="D163" authorId="0" shapeId="0" xr:uid="{F61BC170-6314-4BE8-BD27-ACBE21EC6D83}">
       <text>
         <r>
           <rPr>
@@ -5939,7 +6007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{67EC6033-7BEB-4400-84EE-0A8533A907FD}">
+    <comment ref="E163" authorId="0" shapeId="0" xr:uid="{F2F9EF38-F3FC-4F8C-BAEA-4602406D7D4B}">
       <text>
         <r>
           <rPr>
@@ -5954,7 +6022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{E94FC89C-5249-427A-BE28-D6BFC2F81758}">
+    <comment ref="F163" authorId="0" shapeId="0" xr:uid="{03156B19-EF6A-4B80-952F-EA4B39906AB2}">
       <text>
         <r>
           <rPr>
@@ -5969,7 +6037,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{AA56A34D-E716-48F4-B898-FA37D2EF7D4D}">
+    <comment ref="G163" authorId="0" shapeId="0" xr:uid="{6C70B7FC-07DB-4AA6-AD5D-BA8D185F69A2}">
       <text>
         <r>
           <rPr>
@@ -5984,7 +6052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{90492BA0-E368-47BA-98D1-DF7E39D86EF5}">
+    <comment ref="H163" authorId="0" shapeId="0" xr:uid="{ECCF229F-BC05-441A-A8EC-996A647C989C}">
       <text>
         <r>
           <rPr>
@@ -5999,7 +6067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{9CD81021-C7F5-4F80-9E36-5A372FBC35BF}">
+    <comment ref="D165" authorId="0" shapeId="0" xr:uid="{853363A1-995D-434E-99B9-CBFFCC587E17}">
       <text>
         <r>
           <rPr>
@@ -6015,7 +6083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{49DF1121-32A1-4036-AEE8-BCAAA6147B06}">
+    <comment ref="E165" authorId="0" shapeId="0" xr:uid="{D7049EC9-BADF-40DE-979A-0A74E0293BB1}">
       <text>
         <r>
           <rPr>
@@ -6031,7 +6099,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{9499DF21-B57E-420A-A749-CC9BF2D4D725}">
+    <comment ref="F165" authorId="0" shapeId="0" xr:uid="{C916B5A2-27DC-436D-B575-9210A24C214D}">
       <text>
         <r>
           <rPr>
@@ -6047,7 +6115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{4524A951-07DC-487B-A233-43D4EAAEC701}">
+    <comment ref="G165" authorId="0" shapeId="0" xr:uid="{D9F9FF7F-8008-4D79-ABB3-028FF22CD559}">
       <text>
         <r>
           <rPr>
@@ -6063,7 +6131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{889D9E25-29F0-4C18-931F-58D4600ECBE1}">
+    <comment ref="H165" authorId="0" shapeId="0" xr:uid="{D7D5CD6A-B8A4-4771-AAA0-5113E0A3BC1F}">
       <text>
         <r>
           <rPr>
@@ -6079,7 +6147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{678FE956-BF94-4DA4-81E3-20DDE72682D7}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{06B708C5-CF4C-4BD9-A112-999F5C581700}">
       <text>
         <r>
           <rPr>
@@ -6094,7 +6162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{6CE9DBC0-F411-450C-ADE5-6FE43AB51348}">
+    <comment ref="E167" authorId="0" shapeId="0" xr:uid="{652C7700-A4E9-41DE-B7A6-091614D48006}">
       <text>
         <r>
           <rPr>
@@ -6109,7 +6177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{F2C8AB55-E76F-4187-99C2-69AB2BD9809A}">
+    <comment ref="F167" authorId="0" shapeId="0" xr:uid="{C648195E-E2CA-46F6-BED8-ABE76E4EB10D}">
       <text>
         <r>
           <rPr>
@@ -6124,7 +6192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{D025E63E-9D67-4225-8627-D53B10AA6DB9}">
+    <comment ref="G167" authorId="0" shapeId="0" xr:uid="{876F0647-9D39-464F-9AEF-66CCB9E7BEE5}">
       <text>
         <r>
           <rPr>
@@ -6139,7 +6207,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{E220EC8B-3A48-4133-BD12-15E3EB9F00B6}">
+    <comment ref="H167" authorId="0" shapeId="0" xr:uid="{A2FD75B6-2FF3-4112-A257-87C89428A222}">
       <text>
         <r>
           <rPr>
@@ -6154,7 +6222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{74D29CD4-44A4-4706-B0D2-5EBDC4B70B6C}">
+    <comment ref="D169" authorId="1" shapeId="0" xr:uid="{17B0E3BD-602F-47AD-8FDA-505C553A7C4F}">
       <text>
         <r>
           <rPr>
@@ -9905,7 +9973,7 @@
       <c r="A63" s="4"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SyY+yYxub14M8EISY61nUvK/SDRIDeRj52JE+8io2qWHOKYBDcniHnnBMWj04Dg6A9xXPGPuxcMOEQq3LgpgPw==" saltValue="PkEgSUNpAZnDUgm2gBmAMg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ND4SLoh4PVo8WBSV6JpUjqQNzWYL4oJTcpuugBUajsp0gX6ZNFe/qIzXlBYUogGMsZ7ziGude5wAXl6EEFTIJQ==" saltValue="oG/YMRMXelrw21U67rdCrQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10830,7 +10898,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tz9x8Q/qGt8GvXFcgov/i1jV9i+0SN280vWQ1Wi2MfAmQpTe1KDIxuz3gfdWfR2JyyzlyrG0TX9cX79e1FoD0g==" saltValue="f68PBiazG33+pCHOtO6fLA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="6k8balCNqeu/jNsOnTIrX3cQChPM4O4LlIGPgiasvCJBH72aVLZv5rPfiIMdRMxhCvZU/B548q7JAm7DOoE4dw==" saltValue="/9TA2Ies5mLHcfvu3ubhjg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -10983,7 +11051,7 @@
       <c r="C20" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OWLv4wt7eZfpTkjylLS8CZ5dOqD4LGXi9tTqU/VBltTG0k5Me4AZEu2VHeHMR2EkiPfHm2bZxaywAgGprVvPRQ==" saltValue="nv7A48PRiIriukx8gWd3FA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="X06FtblEHSMGVjAkwg6lh2uvL0/azM2ts/sXbAmzP9LbIqGnmpjvjfNLtaS1IdYoMAn2rgn2hjObNh4OMvN8iw==" saltValue="6pXpQIGCGD0ikfgLv7Nvjw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -11081,7 +11149,7 @@
       <c r="A19" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="A1HxmpYAHEttHBQWHG342QVYWiArFykjwer+ZFmYAYuDuAwfD6dWDoK4QLhwgRG2j1NVmEige2bAdzN/2iRmBw==" saltValue="0MASi91nEUPyIVDjEHc2JQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ZLuonsUbJjE98fgxhVroZRlZKByxzmriSdE0RpjkU7umWhTYMK4dJx+2LJLflEI731+EFmNMlKxyWdCfIm35RA==" saltValue="wlPiINWH2KYx6i1nePc2TA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -11191,7 +11259,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="X3qwrwaHxW/tfJYs6Gqz1499ivQYeZqolDyk3Pz04TdAUUXC0j7NeL+2NE4x26DlyK9YAFW/UEsjfr0xndtjMg==" saltValue="60I3AqrzRq6H4A5EP63h2A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="zUu0DbGje9rxQEujOPipjGXAqKyR+zqaqDlbaZODrK8WW3RdMs7fc1V5+L9jOJuJYdM+6S+MbERYRtfAOPrxpg==" saltValue="/ccHXx9s+8zaKjOWlHJyzQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12949,7 +13017,7 @@
       <c r="B40" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="l3biv7fDkCLC7WcGWsoACMzn4K7tfYBlxw75pzORBfLJSvvXSeeoy6PpbD1gyqfP1EfI70hp4OvbdjUEBUilKQ==" saltValue="qOWs5aWwmMqZWct6LeLgNg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JRXxzWQSew9XWuwM64PC646vLuQwljm1L2uZVPkgOUPt9kxBQOZ7Sh0MyYKzf+dZrB3bUShJSbjDmOSLPm7D9g==" saltValue="ePx7TE3UAarQLX3S6UR2RQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
 </worksheet>
@@ -12982,7 +13050,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JJPoY1gQy+5Zjya+oJyGVJWyk7xIossohLllLv0bQExjH7qNP/odNbRkVwMOuUoysLU3J5C2PFa0v5ImamMZQQ==" saltValue="vlFPm6uDHchKjLI5bqV4vQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="wkZ7gls5XLqtVAdkZ/UhIiwtAM4oYa2nulJzwtiXkP28rhrJ1gkcoYfH+ZLgCyfOlHaN+MFSMQb/CsnkljeKzQ==" saltValue="idc+kSbAHnbknFVKsGpJSQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13183,7 +13251,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7xY0eh2TbIaz6cYFqMGdqfZLDTeKHHV3sUjXMM80ytLF79PrF4Twa43nGTGXnMsG2o3aSOCJhJyo4cJoyA4I1A==" saltValue="GvnTLv+hQvvL2ndE9TFBNw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dc1ArPQ6R6YvK8Jmrd8tzEOS1JJpyZ4PR6YMGjwix1vBT/AqHD3NGV7XAdXQbMBK1Y9KUSVKM0FcfGXlIpr4Ug==" saltValue="3dqEaCgWWfkfCD6GAsgNAw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -14993,7 +15061,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BOKhUe7NLO07DTOCR8ZZ8GjVR3eb5E2p28Ih4LcLWtco/YvmstOElf5E/xLB3t+5DRccHFAsR7rY7iGm4nwuBQ==" saltValue="SRrMV3s1iC7mGcMLbnYxJw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1Vv/C1PnQIArDVX1taWSOPHl4VXUVZql11oD/hVPiBrqnCqWDmOT2C7JbfU+wc++GVEtsnnqcpBTxJ9m/o0lRg==" saltValue="RvyommaYHdChMG38DiLAdw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15804,7 +15872,7 @@
       <c r="L39" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tTDN4mu6UuB8GPIr+B6vANd8U8tSDQ3HjCgmIgL0Jo1cSaEKshRdrlw6vx8BpaiuXJr7j4ZDRlAv9ModHtviDw==" saltValue="pPoz4K5cwbc1s5tzfb5YQg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JFTSavuVfhQ0EhMRMtsw+ivbDo0efkaclF05HYoZt5/2SPofvc3l2pJEyreOXKKFxdjpONTHXr9YqHrkuSSApA==" saltValue="cFWLxDcx+/O3g14V3OWaXw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16197,7 +16265,7 @@
       <c r="L14" s="114"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4TwppDqkGjIElarKsX4N0BGWQsATxT9yEvQiKTXcZZo6hN9BmeNNQgYD/D2wPMMS+c0xy2uEMOicvkvg4PNxhw==" saltValue="CEGRRoC1qwlYzrZuaKUnxQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="05txOTl4YMNj/4JNfeqq79dYaOZmTonGaogsWeeMgcTwoNUpuTKaX5bvr5foXmDulat9LNR3I6GA+dXuDCq6YQ==" saltValue="NKjVQ8voyExfL6R0/i1Wdw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17046,7 +17114,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ubUDLNkJ40cl5AgX24u1kmmUthhGifY2gT6tLIZtjUMa6DIjNnaX4uA5X+cRPL8zGxryP34QneC0edmtDGp3aQ==" saltValue="amNPVPpwykjk/wWCDdSuIg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/nnf0QlRVSRKe0efZTH7Ux+G33jJ4LFA2Y8UwDB7TgACy146UwF7glhG9+pVSg/5So8/0CcZF6pdFOOq/WyeKQ==" saltValue="+7YajI7vhctR3cRmLEJlTg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <conditionalFormatting sqref="B2:I16 B17:C17 E17:I17 B18:I40">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>$A2=""</formula>
@@ -20843,21 +20911,24 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="C+U5aXSRpg4hBSwIuvp3gOvo2YoQnP9nJtyDRfASCsW/5GXTvgrw4Ig3pEgQqQXVLh3mvlt2nI0mrVPP4imspA==" saltValue="/B0ihg7AZGesspc9+xQHeg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fxVDfWSS0tY2zlnP/Yn0mUkJS2QtbUXv6Z/EL3+SzKObZwL/Zayl155Spflxm0CYrDF57kLbCxup07wuKa6FtA==" saltValue="qPLetUDj3pe506Kc89ObMg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B28:B30"/>
     <mergeCell ref="B154:B156"/>
     <mergeCell ref="B64:B66"/>
     <mergeCell ref="B95:B97"/>
@@ -20874,22 +20945,19 @@
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B128:B130"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="B89:B91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -21990,7 +22058,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7B+vzKJEkV/MOEMGMIherWCi/oeoipuPz370rR3tlYP0d1Xz5ZYcXL823pZSE8A5sIVgf/NkIpLew055MOEVIw==" saltValue="Fb3NQ49TJvCIMoYPZ7RlNw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IoTL5cvDrA4k8lthByPX74ZS42+2f5bkhO3YwFukJxiad8d8HK++XMVLEIeJ2Qb15GXu1YpjLQUl2u0T49Vadw==" saltValue="1DSsyRJNeTTUQh4ksS8q7g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -22931,7 +22999,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/ZoxQstB7Qg9l7McbO9bI67NGV4g42eHlrvQqCyZQX+efZlXblyLUgn40dQy8CH5zSUBhGzAAh0IUkhTQAv0EQ==" saltValue="sV+TI60uOKAB1hsamJtmNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tqneieNEOmhbdwpZfDgrHhBeL2K3w4+y0kkDSioB1foq1f9dyvHXi40m/9VYvTKDbChUUkeMcSbnmE5R4/KAOQ==" saltValue="XQ7Y+xY7+edz9DwHEsJdQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -24147,7 +24215,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uao21LeVBhZLb54e0fZHQPGrTjq4XM1Q51neQ3kusq5a+QMhZXDTde7BvINfT6sw3UHRpKGqM/Y14ntOi+peCQ==" saltValue="NaX72LylKYJofhpBVxh2Og==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QSUwCiunsYBgPGaAGREdUt01pWe4SydfLmELcWkb9FVI575xNCPOhy6pblOQiQgKwZP+xD6Eat3KTibjz9M+rQ==" saltValue="nhtPNfDy1SVG2VaF0OkzVg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -32282,7 +32350,7 @@
       <c r="I328" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QeT2A/3rVxJKDTpM8kTqBfsR1cx5mjB75AMD7T4RDidNXRlepO0PMU4MTB0TrpicrMMAABTXquVTRMsVpVDZ2A==" saltValue="qm6UkboDtbH7/dTIWL2Ptw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="rgZ6v0+2P9jAHCArWpwJrQgbCrN+lfTWkMLTMUBvGf3iGrYxWz7Gwr+Db82OFRSmW+0LT8VkSmgZcV2dedZqwA==" saltValue="xxJfXFvLQBJvaXtferGYtw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -33576,16 +33644,16 @@
         <v>1</v>
       </c>
       <c r="L33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="M33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="N33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="O33" s="90">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -33783,16 +33851,20 @@
         <v>1</v>
       </c>
       <c r="L37" s="90">
-        <v>1</v>
+        <f>L31</f>
+        <v>0.38</v>
       </c>
       <c r="M37" s="90">
-        <v>1</v>
+        <f>M31</f>
+        <v>0.38</v>
       </c>
       <c r="N37" s="90">
-        <v>1</v>
+        <f>N31</f>
+        <v>0.38</v>
       </c>
       <c r="O37" s="90">
-        <v>1</v>
+        <f>O31</f>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -34714,16 +34786,20 @@
         <v>1</v>
       </c>
       <c r="L60" s="90">
-        <v>1</v>
+        <f>L54</f>
+        <v>0.7</v>
       </c>
       <c r="M60" s="90">
-        <v>1</v>
+        <f t="shared" ref="M60:O60" si="16">M54</f>
+        <v>0.7</v>
       </c>
       <c r="N60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
       <c r="O60" s="90">
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -34745,39 +34821,39 @@
         <v>0.44</v>
       </c>
       <c r="G61" s="90">
-        <f t="shared" ref="G61:O61" si="16">IF(G15=1,1,G15*1.05)</f>
+        <f t="shared" ref="G61:O61" si="17">IF(G15=1,1,G15*1.05)</f>
         <v>1</v>
       </c>
       <c r="H61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="I61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="J61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="K61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="N61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="O61" s="90">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
     </row>
@@ -34792,11 +34868,11 @@
         <v>202</v>
       </c>
       <c r="C64" s="90">
-        <f t="shared" ref="C64:D67" si="17">IF(C18=1,1,C18*1.05)</f>
+        <f t="shared" ref="C64:D67" si="18">IF(C18=1,1,C18*1.05)</f>
         <v>1</v>
       </c>
       <c r="D64" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E64" s="90">
@@ -34838,11 +34914,11 @@
         <v>203</v>
       </c>
       <c r="C65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D65" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E65" s="90">
@@ -34884,11 +34960,11 @@
         <v>204</v>
       </c>
       <c r="C66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D66" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E66" s="90">
@@ -34930,11 +35006,11 @@
         <v>212</v>
       </c>
       <c r="C67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D67" s="90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E67" s="90">
@@ -34972,7 +35048,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Dw5BGUGQDL0K2R0BQ+Fy90LkBPHC2MbO1KpKqzFK52p8X80YKXouc+YVmOANRPD5HsbhN7dUUC51AqZki33goA==" saltValue="Ex9w9r6vlGlSqr/pnxFlTQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0DX9H+lBVRNKBOJucRXtS18v+uwq5NcJApxMrJm8cSXw4O0NSUWut8qF84RcAI7ood1SkWcnXFQREAXMutT7HQ==" saltValue="dEqpih8hnHTs9W4XyHHTiQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -35254,7 +35330,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jC6/CShUIEp/H43+hmChB2hA86Jv+ewQCgUuj1ha5HqqckM/zV+ldG0hrqgcQalVdHoq8iwqSkBcsJbLHqrr2g==" saltValue="SWvnx9SOJrdYTK30xKC62g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yYRXH+cA53Kb4Jh0Kk/O7SuC9WhVe/F07GAO/U62OvZReoNvv1UbWpB6RsfREaOqos0q9TJIHeqmKQC2mH2bOQ==" saltValue="SjDVStnmNxJJA6VrzeMCnw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
@@ -39114,7 +39190,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/oqgg286IZKUc1dLCjKyq/YLuJcjr5YSQqdZnsuDcjwpE9a4ipAn5A5dQZdZU4kwwROTCorLWeAUopm8cgB8uA==" saltValue="eEsQBaG+3CsmduzVEtU63g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="LqhBMbK6/hiamZmoyHcxUB/bvj/TqP/c1kIJE95fIZQvwvSVLZ2ZEBfjeS9fXDRvIKx/AwvqvccP2ZKUnxq0cw==" saltValue="MFaP4ucjjL6ez+u1BUVTPg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -39754,7 +39830,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="5ThY10ihhgdiFFYmO05qMz9YiBjaVsejfzTfAPQRlfbpUP5/aoj9bcPT25G/HYw0BEW8nvEM8NIxc0kyiOHGjA==" saltValue="63r12bi7g5OyWZ75vzo3Pg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="M9dfNlqXbDtnYkhBD6E9+0/f9ehj5SuhUoJ+H4b6Io0HOd6kGoBIJ3XEEO0+DKZpSm/dbyF7/ekW3KR6Q736uA==" saltValue="bRaeYmihgeop2SGGqwpH/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -40187,7 +40263,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="d4bhtPcM0+m4b7m5Dl0KK0g2E9zsct8gn7pyXxGJuiSN0thmw6PJ9QrILMXi5SnIDSSFqT+YVRhrE9yhpTGMgA==" saltValue="AY0h5qH/a5UJYV8+DdZcsg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9x4j6+urRal23eQEoPawcXxWzlvCLAvimQ1vjY0RAcFJn8w/S1OsUveWpKI0rtW0/ipJVygy9rZ9rwOg9V4qkA==" saltValue="ETPF4CTfL0WfI5/5lWp71A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="69" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40606,7 +40682,7 @@
       <c r="G17" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nZfLd/BZXEX/jCZon+rp2zaLXEGCZ7AMeubtJUwhYQ+ysSdBACSb+s97+AepWyk0qDG5gPI1DpDFgMnXDSSyhg==" saltValue="KS3i6xPuEQqi9oMPJmPH3Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vZHp4xJPVZj3wTRBYeTfvWKrltTxVvn6YKerggP0XOnUoYasTrJoS5v0iVIxh5IuJzk/q7P0l9AiMerD1LuuqQ==" saltValue="vqST9dCw8r/7o+ZaRVPRJw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <legacyDrawing r:id="rId1"/>
@@ -40738,7 +40814,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vYVSv+bqjR3lRhqJ3n9bmaNMT3euSwYOK5tjAbIjNTXjAaCUyWjdP2E3NxENQt34QFFpuA+PG4U0Vlwq8B9SqQ==" saltValue="fqh9YD1DxJ26CJ3Q3MY7Cw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kOmGQK12BEM1bDK7Im2dWnSLTHB+8xt0jddJtOtw8iUvr1102P70LqLlTrWp0oxmP+1yW2L+gwp5VKb+ErtAxw==" saltValue="m5tEwf7C6gloi2WsR/JT+w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -40939,7 +41015,7 @@
       <c r="K14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="moRQDDJw5Ylmw5Kg5/EC7PBUJJpjlM2M9sx7Erq3S4kLRI4RvIahjL6JQopmYktpoVB6/Gt07U+ASzqB8jcpoQ==" saltValue="ijCK0tYVTtwrb04VbRYSyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0yBrSLgiXve1/f0t0pdX/8D8lqAoQp0MMA2+7/zLTB5/pAuCUBMARB1RnZgxZi0CBAlhIECks8GY6oyPgGYEHQ==" saltValue="JSTqPCtkJ+OnJyXRY/YQXw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="193" orientation="portrait"/>
 </worksheet>
@@ -41464,7 +41540,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="C+A5C34/grXkMxrk5NSd0fB8JYdDXapZticGU019eBgtsOlAfaZ21rsw4cfaZ5n9Wp1gaMemCI5KzTrluaM5Mw==" saltValue="iaTSJF2mGG3hRk8ncGN1lw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gOLl2tPHzckxWWim6WcIUcn9KAgkyKOhaggc0RM6bu6UGd+bTWUL2uXD36iBN+kwCKIrprLXjz7ERINKh//qWw==" saltValue="7t/22nej/+DPShm8Y/4Fjg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -41723,7 +41799,7 @@
       <c r="E21" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yJq/C/+HrBr9ncsPqkg9VBp/7xFDwvHWo6e93t83ta/mDG4pInCXyE2kSpIZjep6f4BwUK64ym0ProMt0tfXCg==" saltValue="p5seYcb6zquXXzSPN/7FxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HvHJUHplG+IY94aoLCzv8fxVmxzNRpcS4+56RCK5yfdi77b5YXlmujC3jqUZUBYPBdk0mJzFGnhg0MipJOPvCw==" saltValue="K1ZxbJUD8cLieg0puEUcQA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -41782,23 +41858,24 @@
       <c r="D3" s="47"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ydA1ST/69MkM19WdW/lOrC9SM3OZ9hjjPfd/f1h0QRwLdtj/0uNNEVoMQY/FQ93QnWWx0gt35ogZnKDYhYiCaA==" saltValue="ZJeO2heaVzEOOwnsJxwf7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dC6qf4jDYW54dtJnsQtrQqh07mtyTSBkwfJtrXTzuKF0Adr939AP1JENgGPGcqE/Qu6QGClJpoyLpDkTzvqHDg==" saltValue="3GXQK9HEsbosa5clD/1+XQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f77cb9dc30d15950233dec29875e7d3d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c7972fb108f377c3e0c6a81e726e76be" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="57ec1f31440e439775915f75cb7954ca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="62245b0892ab2a20b5f44f74e1fbf663" ns2:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -41981,25 +42058,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AE9A51-FA73-431C-A4D5-36C1DFA1FEFD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB7E161-F495-494F-94F7-37757C779909}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -42017,11 +42095,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1364B1-D0AC-4AFC-8837-019122E84913}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA00B2B-FC7F-4ED6-BC3D-3DE83488E245}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>